--- a/EXAMPLE/synthetic_ecg_5min.xlsx
+++ b/EXAMPLE/synthetic_ecg_5min.xlsx
@@ -4,6 +4,7 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="RR Intervals" sheetId="1" r:id="rId1"/>
+    <sheet name="Analysis" sheetId="2" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
@@ -4534,4 +4535,5330 @@
     <ignoredError numberStoredAsText="1" sqref="A1:C375"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D383"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" customWidth="1"/>
+    <col min="4" max="4" width="8.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>HRVey 5-min analysis</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>subject_id</v>
+      </c>
+      <c r="B2" t="str">
+        <v>ZK-ECG000</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>date</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2016-10-16</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>sensitivity</v>
+      </c>
+      <c r="B4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>samples</v>
+      </c>
+      <c r="B5">
+        <v>600503</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>source_pdf</v>
+      </c>
+      <c r="B6" t="str">
+        <v>synthetic_ecg_5min</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>beat</v>
+      </c>
+      <c r="B8" t="str">
+        <v>sample</v>
+      </c>
+      <c r="C8" t="str">
+        <v>time_s</v>
+      </c>
+      <c r="D8" t="str">
+        <v>tag</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9">
+        <v>2000</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>2</v>
+      </c>
+      <c r="B10">
+        <v>3640</v>
+      </c>
+      <c r="C10">
+        <v>1.82</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>3</v>
+      </c>
+      <c r="B11">
+        <v>5330</v>
+      </c>
+      <c r="C11">
+        <v>2.665</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>4</v>
+      </c>
+      <c r="B12">
+        <v>7000</v>
+      </c>
+      <c r="C12">
+        <v>3.5</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>5</v>
+      </c>
+      <c r="B13">
+        <v>8630</v>
+      </c>
+      <c r="C13">
+        <v>4.315</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>6</v>
+      </c>
+      <c r="B14">
+        <v>10230</v>
+      </c>
+      <c r="C14">
+        <v>5.115</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>7</v>
+      </c>
+      <c r="B15">
+        <v>11770</v>
+      </c>
+      <c r="C15">
+        <v>5.885</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>8</v>
+      </c>
+      <c r="B16">
+        <v>13300</v>
+      </c>
+      <c r="C16">
+        <v>6.65</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>9</v>
+      </c>
+      <c r="B17">
+        <v>14860</v>
+      </c>
+      <c r="C17">
+        <v>7.43</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>10</v>
+      </c>
+      <c r="B18">
+        <v>16380</v>
+      </c>
+      <c r="C18">
+        <v>8.19</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>11</v>
+      </c>
+      <c r="B19">
+        <v>17950</v>
+      </c>
+      <c r="C19">
+        <v>8.975</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>12</v>
+      </c>
+      <c r="B20">
+        <v>19580</v>
+      </c>
+      <c r="C20">
+        <v>9.79</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>13</v>
+      </c>
+      <c r="B21">
+        <v>21250</v>
+      </c>
+      <c r="C21">
+        <v>10.625</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>14</v>
+      </c>
+      <c r="B22">
+        <v>22940</v>
+      </c>
+      <c r="C22">
+        <v>11.47</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>15</v>
+      </c>
+      <c r="B23">
+        <v>24580</v>
+      </c>
+      <c r="C23">
+        <v>12.29</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>16</v>
+      </c>
+      <c r="B24">
+        <v>26210</v>
+      </c>
+      <c r="C24">
+        <v>13.105</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>17</v>
+      </c>
+      <c r="B25">
+        <v>27820</v>
+      </c>
+      <c r="C25">
+        <v>13.91</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>18</v>
+      </c>
+      <c r="B26">
+        <v>29330</v>
+      </c>
+      <c r="C26">
+        <v>14.665</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>19</v>
+      </c>
+      <c r="B27">
+        <v>30840</v>
+      </c>
+      <c r="C27">
+        <v>15.42</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>20</v>
+      </c>
+      <c r="B28">
+        <v>32320</v>
+      </c>
+      <c r="C28">
+        <v>16.16</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>21</v>
+      </c>
+      <c r="B29">
+        <v>33850</v>
+      </c>
+      <c r="C29">
+        <v>16.925</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>22</v>
+      </c>
+      <c r="B30">
+        <v>35410</v>
+      </c>
+      <c r="C30">
+        <v>17.705</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>23</v>
+      </c>
+      <c r="B31">
+        <v>37050</v>
+      </c>
+      <c r="C31">
+        <v>18.525</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>24</v>
+      </c>
+      <c r="B32">
+        <v>38690</v>
+      </c>
+      <c r="C32">
+        <v>19.345</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>25</v>
+      </c>
+      <c r="B33">
+        <v>40380</v>
+      </c>
+      <c r="C33">
+        <v>20.19</v>
+      </c>
+      <c r="D33" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>26</v>
+      </c>
+      <c r="B34">
+        <v>42030</v>
+      </c>
+      <c r="C34">
+        <v>21.015</v>
+      </c>
+      <c r="D34" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>27</v>
+      </c>
+      <c r="B35">
+        <v>43632</v>
+      </c>
+      <c r="C35">
+        <v>21.816</v>
+      </c>
+      <c r="D35" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>28</v>
+      </c>
+      <c r="B36">
+        <v>45132</v>
+      </c>
+      <c r="C36">
+        <v>22.566</v>
+      </c>
+      <c r="D36" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>29</v>
+      </c>
+      <c r="B37">
+        <v>46643</v>
+      </c>
+      <c r="C37">
+        <v>23.322</v>
+      </c>
+      <c r="D37" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>30</v>
+      </c>
+      <c r="B38">
+        <v>48163</v>
+      </c>
+      <c r="C38">
+        <v>24.082</v>
+      </c>
+      <c r="D38" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>31</v>
+      </c>
+      <c r="B39">
+        <v>49712</v>
+      </c>
+      <c r="C39">
+        <v>24.856</v>
+      </c>
+      <c r="D39" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>32</v>
+      </c>
+      <c r="B40">
+        <v>51252</v>
+      </c>
+      <c r="C40">
+        <v>25.626</v>
+      </c>
+      <c r="D40" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>33</v>
+      </c>
+      <c r="B41">
+        <v>52872</v>
+      </c>
+      <c r="C41">
+        <v>26.436</v>
+      </c>
+      <c r="D41" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>34</v>
+      </c>
+      <c r="B42">
+        <v>54512</v>
+      </c>
+      <c r="C42">
+        <v>27.256</v>
+      </c>
+      <c r="D42" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>35</v>
+      </c>
+      <c r="B43">
+        <v>56172</v>
+      </c>
+      <c r="C43">
+        <v>28.086</v>
+      </c>
+      <c r="D43" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>36</v>
+      </c>
+      <c r="B44">
+        <v>57862</v>
+      </c>
+      <c r="C44">
+        <v>28.931</v>
+      </c>
+      <c r="D44" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>37</v>
+      </c>
+      <c r="B45">
+        <v>59472</v>
+      </c>
+      <c r="C45">
+        <v>29.736</v>
+      </c>
+      <c r="D45" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>38</v>
+      </c>
+      <c r="B46">
+        <v>61053</v>
+      </c>
+      <c r="C46">
+        <v>30.527</v>
+      </c>
+      <c r="D46" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>39</v>
+      </c>
+      <c r="B47">
+        <v>62622</v>
+      </c>
+      <c r="C47">
+        <v>31.311</v>
+      </c>
+      <c r="D47" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>40</v>
+      </c>
+      <c r="B48">
+        <v>64123</v>
+      </c>
+      <c r="C48">
+        <v>32.062</v>
+      </c>
+      <c r="D48" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>41</v>
+      </c>
+      <c r="B49">
+        <v>65212</v>
+      </c>
+      <c r="C49">
+        <v>32.606</v>
+      </c>
+      <c r="D49" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>42</v>
+      </c>
+      <c r="B50">
+        <v>67712</v>
+      </c>
+      <c r="C50">
+        <v>33.856</v>
+      </c>
+      <c r="D50" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>43</v>
+      </c>
+      <c r="B51">
+        <v>68822</v>
+      </c>
+      <c r="C51">
+        <v>34.411</v>
+      </c>
+      <c r="D51" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>44</v>
+      </c>
+      <c r="B52">
+        <v>70442</v>
+      </c>
+      <c r="C52">
+        <v>35.221</v>
+      </c>
+      <c r="D52" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>45</v>
+      </c>
+      <c r="B53">
+        <v>72122</v>
+      </c>
+      <c r="C53">
+        <v>36.061</v>
+      </c>
+      <c r="D53" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>46</v>
+      </c>
+      <c r="B54">
+        <v>73832</v>
+      </c>
+      <c r="C54">
+        <v>36.916</v>
+      </c>
+      <c r="D54" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>47</v>
+      </c>
+      <c r="B55">
+        <v>75442</v>
+      </c>
+      <c r="C55">
+        <v>37.721</v>
+      </c>
+      <c r="D55" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>48</v>
+      </c>
+      <c r="B56">
+        <v>77063</v>
+      </c>
+      <c r="C56">
+        <v>38.532</v>
+      </c>
+      <c r="D56" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>49</v>
+      </c>
+      <c r="B57">
+        <v>78632</v>
+      </c>
+      <c r="C57">
+        <v>39.316</v>
+      </c>
+      <c r="D57" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>50</v>
+      </c>
+      <c r="B58">
+        <v>80142</v>
+      </c>
+      <c r="C58">
+        <v>40.071</v>
+      </c>
+      <c r="D58" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>51</v>
+      </c>
+      <c r="B59">
+        <v>81712</v>
+      </c>
+      <c r="C59">
+        <v>40.856</v>
+      </c>
+      <c r="D59" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>52</v>
+      </c>
+      <c r="B60">
+        <v>83272</v>
+      </c>
+      <c r="C60">
+        <v>41.636</v>
+      </c>
+      <c r="D60" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>53</v>
+      </c>
+      <c r="B61">
+        <v>84823</v>
+      </c>
+      <c r="C61">
+        <v>42.412</v>
+      </c>
+      <c r="D61" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>54</v>
+      </c>
+      <c r="B62">
+        <v>86447</v>
+      </c>
+      <c r="C62">
+        <v>43.224</v>
+      </c>
+      <c r="D62" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>55</v>
+      </c>
+      <c r="B63">
+        <v>88136</v>
+      </c>
+      <c r="C63">
+        <v>44.068</v>
+      </c>
+      <c r="D63" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>56</v>
+      </c>
+      <c r="B64">
+        <v>89807</v>
+      </c>
+      <c r="C64">
+        <v>44.904</v>
+      </c>
+      <c r="D64" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>57</v>
+      </c>
+      <c r="B65">
+        <v>91487</v>
+      </c>
+      <c r="C65">
+        <v>45.744</v>
+      </c>
+      <c r="D65" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>58</v>
+      </c>
+      <c r="B66">
+        <v>93117</v>
+      </c>
+      <c r="C66">
+        <v>46.559</v>
+      </c>
+      <c r="D66" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>59</v>
+      </c>
+      <c r="B67">
+        <v>94716</v>
+      </c>
+      <c r="C67">
+        <v>47.358</v>
+      </c>
+      <c r="D67" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>60</v>
+      </c>
+      <c r="B68">
+        <v>96287</v>
+      </c>
+      <c r="C68">
+        <v>48.144</v>
+      </c>
+      <c r="D68" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>61</v>
+      </c>
+      <c r="B69">
+        <v>97787</v>
+      </c>
+      <c r="C69">
+        <v>48.894</v>
+      </c>
+      <c r="D69" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>62</v>
+      </c>
+      <c r="B70">
+        <v>99327</v>
+      </c>
+      <c r="C70">
+        <v>49.664</v>
+      </c>
+      <c r="D70" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>63</v>
+      </c>
+      <c r="B71">
+        <v>100877</v>
+      </c>
+      <c r="C71">
+        <v>50.439</v>
+      </c>
+      <c r="D71" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>64</v>
+      </c>
+      <c r="B72">
+        <v>102487</v>
+      </c>
+      <c r="C72">
+        <v>51.244</v>
+      </c>
+      <c r="D72" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>65</v>
+      </c>
+      <c r="B73">
+        <v>104107</v>
+      </c>
+      <c r="C73">
+        <v>52.054</v>
+      </c>
+      <c r="D73" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>66</v>
+      </c>
+      <c r="B74">
+        <v>105776</v>
+      </c>
+      <c r="C74">
+        <v>52.888</v>
+      </c>
+      <c r="D74" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>67</v>
+      </c>
+      <c r="B75">
+        <v>107446</v>
+      </c>
+      <c r="C75">
+        <v>53.723</v>
+      </c>
+      <c r="D75" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>68</v>
+      </c>
+      <c r="B76">
+        <v>109116</v>
+      </c>
+      <c r="C76">
+        <v>54.558</v>
+      </c>
+      <c r="D76" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>69</v>
+      </c>
+      <c r="B77">
+        <v>110746</v>
+      </c>
+      <c r="C77">
+        <v>55.373</v>
+      </c>
+      <c r="D77" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>70</v>
+      </c>
+      <c r="B78">
+        <v>112267</v>
+      </c>
+      <c r="C78">
+        <v>56.134</v>
+      </c>
+      <c r="D78" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>71</v>
+      </c>
+      <c r="B79">
+        <v>113777</v>
+      </c>
+      <c r="C79">
+        <v>56.889</v>
+      </c>
+      <c r="D79" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>72</v>
+      </c>
+      <c r="B80">
+        <v>115316</v>
+      </c>
+      <c r="C80">
+        <v>57.658</v>
+      </c>
+      <c r="D80" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>73</v>
+      </c>
+      <c r="B81">
+        <v>116807</v>
+      </c>
+      <c r="C81">
+        <v>58.404</v>
+      </c>
+      <c r="D81" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>74</v>
+      </c>
+      <c r="B82">
+        <v>118386</v>
+      </c>
+      <c r="C82">
+        <v>59.193</v>
+      </c>
+      <c r="D82" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>75</v>
+      </c>
+      <c r="B83">
+        <v>120016</v>
+      </c>
+      <c r="C83">
+        <v>60.008</v>
+      </c>
+      <c r="D83" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>76</v>
+      </c>
+      <c r="B84">
+        <v>121716</v>
+      </c>
+      <c r="C84">
+        <v>60.858</v>
+      </c>
+      <c r="D84" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>77</v>
+      </c>
+      <c r="B85">
+        <v>123407</v>
+      </c>
+      <c r="C85">
+        <v>61.704</v>
+      </c>
+      <c r="D85" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>78</v>
+      </c>
+      <c r="B86">
+        <v>125067</v>
+      </c>
+      <c r="C86">
+        <v>62.534</v>
+      </c>
+      <c r="D86" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>79</v>
+      </c>
+      <c r="B87">
+        <v>126686</v>
+      </c>
+      <c r="C87">
+        <v>63.343</v>
+      </c>
+      <c r="D87" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>80</v>
+      </c>
+      <c r="B88">
+        <v>128256</v>
+      </c>
+      <c r="C88">
+        <v>64.128</v>
+      </c>
+      <c r="D88" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>81</v>
+      </c>
+      <c r="B89">
+        <v>129824</v>
+      </c>
+      <c r="C89">
+        <v>64.912</v>
+      </c>
+      <c r="D89" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>82</v>
+      </c>
+      <c r="B90">
+        <v>131334</v>
+      </c>
+      <c r="C90">
+        <v>65.667</v>
+      </c>
+      <c r="D90" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>83</v>
+      </c>
+      <c r="B91">
+        <v>132863</v>
+      </c>
+      <c r="C91">
+        <v>66.432</v>
+      </c>
+      <c r="D91" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>84</v>
+      </c>
+      <c r="B92">
+        <v>134433</v>
+      </c>
+      <c r="C92">
+        <v>67.217</v>
+      </c>
+      <c r="D92" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>85</v>
+      </c>
+      <c r="B93">
+        <v>136043</v>
+      </c>
+      <c r="C93">
+        <v>68.022</v>
+      </c>
+      <c r="D93" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>86</v>
+      </c>
+      <c r="B94">
+        <v>137684</v>
+      </c>
+      <c r="C94">
+        <v>68.842</v>
+      </c>
+      <c r="D94" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>87</v>
+      </c>
+      <c r="B95">
+        <v>139343</v>
+      </c>
+      <c r="C95">
+        <v>69.672</v>
+      </c>
+      <c r="D95" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>88</v>
+      </c>
+      <c r="B96">
+        <v>141013</v>
+      </c>
+      <c r="C96">
+        <v>70.507</v>
+      </c>
+      <c r="D96" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>89</v>
+      </c>
+      <c r="B97">
+        <v>142644</v>
+      </c>
+      <c r="C97">
+        <v>71.322</v>
+      </c>
+      <c r="D97" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>90</v>
+      </c>
+      <c r="B98">
+        <v>144274</v>
+      </c>
+      <c r="C98">
+        <v>72.137</v>
+      </c>
+      <c r="D98" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>91</v>
+      </c>
+      <c r="B99">
+        <v>145844</v>
+      </c>
+      <c r="C99">
+        <v>72.922</v>
+      </c>
+      <c r="D99" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>92</v>
+      </c>
+      <c r="B100">
+        <v>147373</v>
+      </c>
+      <c r="C100">
+        <v>73.687</v>
+      </c>
+      <c r="D100" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>93</v>
+      </c>
+      <c r="B101">
+        <v>148913</v>
+      </c>
+      <c r="C101">
+        <v>74.457</v>
+      </c>
+      <c r="D101" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102">
+        <v>94</v>
+      </c>
+      <c r="B102">
+        <v>150453</v>
+      </c>
+      <c r="C102">
+        <v>75.227</v>
+      </c>
+      <c r="D102" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103">
+        <v>95</v>
+      </c>
+      <c r="B103">
+        <v>152063</v>
+      </c>
+      <c r="C103">
+        <v>76.032</v>
+      </c>
+      <c r="D103" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104">
+        <v>96</v>
+      </c>
+      <c r="B104">
+        <v>153694</v>
+      </c>
+      <c r="C104">
+        <v>76.847</v>
+      </c>
+      <c r="D104" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105">
+        <v>97</v>
+      </c>
+      <c r="B105">
+        <v>155383</v>
+      </c>
+      <c r="C105">
+        <v>77.692</v>
+      </c>
+      <c r="D105" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106">
+        <v>98</v>
+      </c>
+      <c r="B106">
+        <v>157033</v>
+      </c>
+      <c r="C106">
+        <v>78.517</v>
+      </c>
+      <c r="D106" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107">
+        <v>99</v>
+      </c>
+      <c r="B107">
+        <v>158703</v>
+      </c>
+      <c r="C107">
+        <v>79.352</v>
+      </c>
+      <c r="D107" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108">
+        <v>100</v>
+      </c>
+      <c r="B108">
+        <v>160283</v>
+      </c>
+      <c r="C108">
+        <v>80.142</v>
+      </c>
+      <c r="D108" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109">
+        <v>101</v>
+      </c>
+      <c r="B109">
+        <v>161813</v>
+      </c>
+      <c r="C109">
+        <v>80.907</v>
+      </c>
+      <c r="D109" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110">
+        <v>102</v>
+      </c>
+      <c r="B110">
+        <v>163334</v>
+      </c>
+      <c r="C110">
+        <v>81.667</v>
+      </c>
+      <c r="D110" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111">
+        <v>103</v>
+      </c>
+      <c r="B111">
+        <v>164834</v>
+      </c>
+      <c r="C111">
+        <v>82.417</v>
+      </c>
+      <c r="D111" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112">
+        <v>104</v>
+      </c>
+      <c r="B112">
+        <v>166373</v>
+      </c>
+      <c r="C112">
+        <v>83.187</v>
+      </c>
+      <c r="D112" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113">
+        <v>105</v>
+      </c>
+      <c r="B113">
+        <v>167993</v>
+      </c>
+      <c r="C113">
+        <v>83.997</v>
+      </c>
+      <c r="D113" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114">
+        <v>106</v>
+      </c>
+      <c r="B114">
+        <v>169584</v>
+      </c>
+      <c r="C114">
+        <v>84.792</v>
+      </c>
+      <c r="D114" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115">
+        <v>107</v>
+      </c>
+      <c r="B115">
+        <v>171224</v>
+      </c>
+      <c r="C115">
+        <v>85.612</v>
+      </c>
+      <c r="D115" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116">
+        <v>108</v>
+      </c>
+      <c r="B116">
+        <v>172912</v>
+      </c>
+      <c r="C116">
+        <v>86.456</v>
+      </c>
+      <c r="D116" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117">
+        <v>109</v>
+      </c>
+      <c r="B117">
+        <v>174592</v>
+      </c>
+      <c r="C117">
+        <v>87.296</v>
+      </c>
+      <c r="D117" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118">
+        <v>110</v>
+      </c>
+      <c r="B118">
+        <v>176232</v>
+      </c>
+      <c r="C118">
+        <v>88.116</v>
+      </c>
+      <c r="D118" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119">
+        <v>111</v>
+      </c>
+      <c r="B119">
+        <v>177823</v>
+      </c>
+      <c r="C119">
+        <v>88.912</v>
+      </c>
+      <c r="D119" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120">
+        <v>112</v>
+      </c>
+      <c r="B120">
+        <v>179393</v>
+      </c>
+      <c r="C120">
+        <v>89.697</v>
+      </c>
+      <c r="D120" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121">
+        <v>113</v>
+      </c>
+      <c r="B121">
+        <v>180932</v>
+      </c>
+      <c r="C121">
+        <v>90.466</v>
+      </c>
+      <c r="D121" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122">
+        <v>114</v>
+      </c>
+      <c r="B122">
+        <v>182432</v>
+      </c>
+      <c r="C122">
+        <v>91.216</v>
+      </c>
+      <c r="D122" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123">
+        <v>115</v>
+      </c>
+      <c r="B123">
+        <v>183973</v>
+      </c>
+      <c r="C123">
+        <v>91.987</v>
+      </c>
+      <c r="D123" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124">
+        <v>116</v>
+      </c>
+      <c r="B124">
+        <v>185572</v>
+      </c>
+      <c r="C124">
+        <v>92.786</v>
+      </c>
+      <c r="D124" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125">
+        <v>117</v>
+      </c>
+      <c r="B125">
+        <v>187182</v>
+      </c>
+      <c r="C125">
+        <v>93.591</v>
+      </c>
+      <c r="D125" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126">
+        <v>118</v>
+      </c>
+      <c r="B126">
+        <v>188853</v>
+      </c>
+      <c r="C126">
+        <v>94.427</v>
+      </c>
+      <c r="D126" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127">
+        <v>119</v>
+      </c>
+      <c r="B127">
+        <v>190513</v>
+      </c>
+      <c r="C127">
+        <v>95.257</v>
+      </c>
+      <c r="D127" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128">
+        <v>120</v>
+      </c>
+      <c r="B128">
+        <v>192202</v>
+      </c>
+      <c r="C128">
+        <v>96.101</v>
+      </c>
+      <c r="D128" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129">
+        <v>121</v>
+      </c>
+      <c r="B129">
+        <v>193822</v>
+      </c>
+      <c r="C129">
+        <v>96.911</v>
+      </c>
+      <c r="D129" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130">
+        <v>122</v>
+      </c>
+      <c r="B130">
+        <v>195402</v>
+      </c>
+      <c r="C130">
+        <v>97.701</v>
+      </c>
+      <c r="D130" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131">
+        <v>123</v>
+      </c>
+      <c r="B131">
+        <v>196922</v>
+      </c>
+      <c r="C131">
+        <v>98.461</v>
+      </c>
+      <c r="D131" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132">
+        <v>124</v>
+      </c>
+      <c r="B132">
+        <v>198442</v>
+      </c>
+      <c r="C132">
+        <v>99.221</v>
+      </c>
+      <c r="D132" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133">
+        <v>125</v>
+      </c>
+      <c r="B133">
+        <v>199922</v>
+      </c>
+      <c r="C133">
+        <v>99.961</v>
+      </c>
+      <c r="D133" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134">
+        <v>126</v>
+      </c>
+      <c r="B134">
+        <v>201463</v>
+      </c>
+      <c r="C134">
+        <v>100.732</v>
+      </c>
+      <c r="D134" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135">
+        <v>127</v>
+      </c>
+      <c r="B135">
+        <v>203092</v>
+      </c>
+      <c r="C135">
+        <v>101.546</v>
+      </c>
+      <c r="D135" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136">
+        <v>128</v>
+      </c>
+      <c r="B136">
+        <v>204693</v>
+      </c>
+      <c r="C136">
+        <v>102.347</v>
+      </c>
+      <c r="D136" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137">
+        <v>129</v>
+      </c>
+      <c r="B137">
+        <v>206393</v>
+      </c>
+      <c r="C137">
+        <v>103.197</v>
+      </c>
+      <c r="D137" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138">
+        <v>130</v>
+      </c>
+      <c r="B138">
+        <v>208023</v>
+      </c>
+      <c r="C138">
+        <v>104.012</v>
+      </c>
+      <c r="D138" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139">
+        <v>131</v>
+      </c>
+      <c r="B139">
+        <v>209683</v>
+      </c>
+      <c r="C139">
+        <v>104.842</v>
+      </c>
+      <c r="D139" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140">
+        <v>132</v>
+      </c>
+      <c r="B140">
+        <v>211262</v>
+      </c>
+      <c r="C140">
+        <v>105.631</v>
+      </c>
+      <c r="D140" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141">
+        <v>133</v>
+      </c>
+      <c r="B141">
+        <v>212832</v>
+      </c>
+      <c r="C141">
+        <v>106.416</v>
+      </c>
+      <c r="D141" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142">
+        <v>134</v>
+      </c>
+      <c r="B142">
+        <v>214353</v>
+      </c>
+      <c r="C142">
+        <v>107.177</v>
+      </c>
+      <c r="D142" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143">
+        <v>135</v>
+      </c>
+      <c r="B143">
+        <v>215833</v>
+      </c>
+      <c r="C143">
+        <v>107.917</v>
+      </c>
+      <c r="D143" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144">
+        <v>136</v>
+      </c>
+      <c r="B144">
+        <v>217413</v>
+      </c>
+      <c r="C144">
+        <v>108.707</v>
+      </c>
+      <c r="D144" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145">
+        <v>137</v>
+      </c>
+      <c r="B145">
+        <v>219043</v>
+      </c>
+      <c r="C145">
+        <v>109.522</v>
+      </c>
+      <c r="D145" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146">
+        <v>138</v>
+      </c>
+      <c r="B146">
+        <v>220683</v>
+      </c>
+      <c r="C146">
+        <v>110.342</v>
+      </c>
+      <c r="D146" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147">
+        <v>139</v>
+      </c>
+      <c r="B147">
+        <v>222344</v>
+      </c>
+      <c r="C147">
+        <v>111.172</v>
+      </c>
+      <c r="D147" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148">
+        <v>140</v>
+      </c>
+      <c r="B148">
+        <v>224023</v>
+      </c>
+      <c r="C148">
+        <v>112.012</v>
+      </c>
+      <c r="D148" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149">
+        <v>141</v>
+      </c>
+      <c r="B149">
+        <v>225654</v>
+      </c>
+      <c r="C149">
+        <v>112.827</v>
+      </c>
+      <c r="D149" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150">
+        <v>142</v>
+      </c>
+      <c r="B150">
+        <v>227303</v>
+      </c>
+      <c r="C150">
+        <v>113.652</v>
+      </c>
+      <c r="D150" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151">
+        <v>143</v>
+      </c>
+      <c r="B151">
+        <v>228854</v>
+      </c>
+      <c r="C151">
+        <v>114.427</v>
+      </c>
+      <c r="D151" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152">
+        <v>144</v>
+      </c>
+      <c r="B152">
+        <v>230393</v>
+      </c>
+      <c r="C152">
+        <v>115.197</v>
+      </c>
+      <c r="D152" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153">
+        <v>145</v>
+      </c>
+      <c r="B153">
+        <v>231893</v>
+      </c>
+      <c r="C153">
+        <v>115.947</v>
+      </c>
+      <c r="D153" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154">
+        <v>146</v>
+      </c>
+      <c r="B154">
+        <v>233413</v>
+      </c>
+      <c r="C154">
+        <v>116.707</v>
+      </c>
+      <c r="D154" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155">
+        <v>147</v>
+      </c>
+      <c r="B155">
+        <v>234953</v>
+      </c>
+      <c r="C155">
+        <v>117.477</v>
+      </c>
+      <c r="D155" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156">
+        <v>148</v>
+      </c>
+      <c r="B156">
+        <v>236603</v>
+      </c>
+      <c r="C156">
+        <v>118.302</v>
+      </c>
+      <c r="D156" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157">
+        <v>149</v>
+      </c>
+      <c r="B157">
+        <v>238254</v>
+      </c>
+      <c r="C157">
+        <v>119.127</v>
+      </c>
+      <c r="D157" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158">
+        <v>150</v>
+      </c>
+      <c r="B158">
+        <v>239963</v>
+      </c>
+      <c r="C158">
+        <v>119.982</v>
+      </c>
+      <c r="D158" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159">
+        <v>151</v>
+      </c>
+      <c r="B159">
+        <v>241633</v>
+      </c>
+      <c r="C159">
+        <v>120.817</v>
+      </c>
+      <c r="D159" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160">
+        <v>152</v>
+      </c>
+      <c r="B160">
+        <v>243253</v>
+      </c>
+      <c r="C160">
+        <v>121.627</v>
+      </c>
+      <c r="D160" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161">
+        <v>153</v>
+      </c>
+      <c r="B161">
+        <v>244834</v>
+      </c>
+      <c r="C161">
+        <v>122.417</v>
+      </c>
+      <c r="D161" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162">
+        <v>154</v>
+      </c>
+      <c r="B162">
+        <v>246373</v>
+      </c>
+      <c r="C162">
+        <v>123.187</v>
+      </c>
+      <c r="D162" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163">
+        <v>155</v>
+      </c>
+      <c r="B163">
+        <v>247894</v>
+      </c>
+      <c r="C163">
+        <v>123.947</v>
+      </c>
+      <c r="D163" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164">
+        <v>156</v>
+      </c>
+      <c r="B164">
+        <v>249413</v>
+      </c>
+      <c r="C164">
+        <v>124.707</v>
+      </c>
+      <c r="D164" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165">
+        <v>157</v>
+      </c>
+      <c r="B165">
+        <v>250953</v>
+      </c>
+      <c r="C165">
+        <v>125.477</v>
+      </c>
+      <c r="D165" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166">
+        <v>158</v>
+      </c>
+      <c r="B166">
+        <v>252514</v>
+      </c>
+      <c r="C166">
+        <v>126.257</v>
+      </c>
+      <c r="D166" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167">
+        <v>159</v>
+      </c>
+      <c r="B167">
+        <v>254143</v>
+      </c>
+      <c r="C167">
+        <v>127.072</v>
+      </c>
+      <c r="D167" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168">
+        <v>160</v>
+      </c>
+      <c r="B168">
+        <v>255853</v>
+      </c>
+      <c r="C168">
+        <v>127.927</v>
+      </c>
+      <c r="D168" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169">
+        <v>161</v>
+      </c>
+      <c r="B169">
+        <v>257507</v>
+      </c>
+      <c r="C169">
+        <v>128.754</v>
+      </c>
+      <c r="D169" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170">
+        <v>162</v>
+      </c>
+      <c r="B170">
+        <v>259137</v>
+      </c>
+      <c r="C170">
+        <v>129.569</v>
+      </c>
+      <c r="D170" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171">
+        <v>163</v>
+      </c>
+      <c r="B171">
+        <v>260766</v>
+      </c>
+      <c r="C171">
+        <v>130.383</v>
+      </c>
+      <c r="D171" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172">
+        <v>164</v>
+      </c>
+      <c r="B172">
+        <v>262367</v>
+      </c>
+      <c r="C172">
+        <v>131.184</v>
+      </c>
+      <c r="D172" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173">
+        <v>165</v>
+      </c>
+      <c r="B173">
+        <v>263866</v>
+      </c>
+      <c r="C173">
+        <v>131.933</v>
+      </c>
+      <c r="D173" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174">
+        <v>166</v>
+      </c>
+      <c r="B174">
+        <v>265377</v>
+      </c>
+      <c r="C174">
+        <v>132.689</v>
+      </c>
+      <c r="D174" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175">
+        <v>167</v>
+      </c>
+      <c r="B175">
+        <v>266897</v>
+      </c>
+      <c r="C175">
+        <v>133.449</v>
+      </c>
+      <c r="D175" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176">
+        <v>168</v>
+      </c>
+      <c r="B176">
+        <v>268427</v>
+      </c>
+      <c r="C176">
+        <v>134.214</v>
+      </c>
+      <c r="D176" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177">
+        <v>169</v>
+      </c>
+      <c r="B177">
+        <v>270067</v>
+      </c>
+      <c r="C177">
+        <v>135.034</v>
+      </c>
+      <c r="D177" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178">
+        <v>170</v>
+      </c>
+      <c r="B178">
+        <v>271727</v>
+      </c>
+      <c r="C178">
+        <v>135.864</v>
+      </c>
+      <c r="D178" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179">
+        <v>171</v>
+      </c>
+      <c r="B179">
+        <v>273407</v>
+      </c>
+      <c r="C179">
+        <v>136.704</v>
+      </c>
+      <c r="D179" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180">
+        <v>172</v>
+      </c>
+      <c r="B180">
+        <v>275066</v>
+      </c>
+      <c r="C180">
+        <v>137.533</v>
+      </c>
+      <c r="D180" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181">
+        <v>173</v>
+      </c>
+      <c r="B181">
+        <v>276707</v>
+      </c>
+      <c r="C181">
+        <v>138.354</v>
+      </c>
+      <c r="D181" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182">
+        <v>174</v>
+      </c>
+      <c r="B182">
+        <v>278287</v>
+      </c>
+      <c r="C182">
+        <v>139.144</v>
+      </c>
+      <c r="D182" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183">
+        <v>175</v>
+      </c>
+      <c r="B183">
+        <v>279836</v>
+      </c>
+      <c r="C183">
+        <v>139.918</v>
+      </c>
+      <c r="D183" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184">
+        <v>176</v>
+      </c>
+      <c r="B184">
+        <v>281327</v>
+      </c>
+      <c r="C184">
+        <v>140.664</v>
+      </c>
+      <c r="D184" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185">
+        <v>177</v>
+      </c>
+      <c r="B185">
+        <v>282826</v>
+      </c>
+      <c r="C185">
+        <v>141.413</v>
+      </c>
+      <c r="D185" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186">
+        <v>178</v>
+      </c>
+      <c r="B186">
+        <v>284407</v>
+      </c>
+      <c r="C186">
+        <v>142.204</v>
+      </c>
+      <c r="D186" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187">
+        <v>179</v>
+      </c>
+      <c r="B187">
+        <v>285997</v>
+      </c>
+      <c r="C187">
+        <v>142.999</v>
+      </c>
+      <c r="D187" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188">
+        <v>180</v>
+      </c>
+      <c r="B188">
+        <v>287647</v>
+      </c>
+      <c r="C188">
+        <v>143.824</v>
+      </c>
+      <c r="D188" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189">
+        <v>181</v>
+      </c>
+      <c r="B189">
+        <v>289317</v>
+      </c>
+      <c r="C189">
+        <v>144.659</v>
+      </c>
+      <c r="D189" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190">
+        <v>182</v>
+      </c>
+      <c r="B190">
+        <v>290987</v>
+      </c>
+      <c r="C190">
+        <v>145.494</v>
+      </c>
+      <c r="D190" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191">
+        <v>183</v>
+      </c>
+      <c r="B191">
+        <v>292627</v>
+      </c>
+      <c r="C191">
+        <v>146.314</v>
+      </c>
+      <c r="D191" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192">
+        <v>184</v>
+      </c>
+      <c r="B192">
+        <v>294257</v>
+      </c>
+      <c r="C192">
+        <v>147.129</v>
+      </c>
+      <c r="D192" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193">
+        <v>185</v>
+      </c>
+      <c r="B193">
+        <v>295817</v>
+      </c>
+      <c r="C193">
+        <v>147.909</v>
+      </c>
+      <c r="D193" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194">
+        <v>186</v>
+      </c>
+      <c r="B194">
+        <v>297346</v>
+      </c>
+      <c r="C194">
+        <v>148.673</v>
+      </c>
+      <c r="D194" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195">
+        <v>187</v>
+      </c>
+      <c r="B195">
+        <v>298866</v>
+      </c>
+      <c r="C195">
+        <v>149.433</v>
+      </c>
+      <c r="D195" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196">
+        <v>188</v>
+      </c>
+      <c r="B196">
+        <v>300423</v>
+      </c>
+      <c r="C196">
+        <v>150.212</v>
+      </c>
+      <c r="D196" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197">
+        <v>189</v>
+      </c>
+      <c r="B197">
+        <v>302022</v>
+      </c>
+      <c r="C197">
+        <v>151.011</v>
+      </c>
+      <c r="D197" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198">
+        <v>190</v>
+      </c>
+      <c r="B198">
+        <v>303652</v>
+      </c>
+      <c r="C198">
+        <v>151.826</v>
+      </c>
+      <c r="D198" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199">
+        <v>191</v>
+      </c>
+      <c r="B199">
+        <v>305302</v>
+      </c>
+      <c r="C199">
+        <v>152.651</v>
+      </c>
+      <c r="D199" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200">
+        <v>192</v>
+      </c>
+      <c r="B200">
+        <v>306952</v>
+      </c>
+      <c r="C200">
+        <v>153.476</v>
+      </c>
+      <c r="D200" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201">
+        <v>193</v>
+      </c>
+      <c r="B201">
+        <v>308642</v>
+      </c>
+      <c r="C201">
+        <v>154.321</v>
+      </c>
+      <c r="D201" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202">
+        <v>194</v>
+      </c>
+      <c r="B202">
+        <v>310293</v>
+      </c>
+      <c r="C202">
+        <v>155.147</v>
+      </c>
+      <c r="D202" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203">
+        <v>195</v>
+      </c>
+      <c r="B203">
+        <v>311882</v>
+      </c>
+      <c r="C203">
+        <v>155.941</v>
+      </c>
+      <c r="D203" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204">
+        <v>196</v>
+      </c>
+      <c r="B204">
+        <v>313442</v>
+      </c>
+      <c r="C204">
+        <v>156.721</v>
+      </c>
+      <c r="D204" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205">
+        <v>197</v>
+      </c>
+      <c r="B205">
+        <v>314982</v>
+      </c>
+      <c r="C205">
+        <v>157.491</v>
+      </c>
+      <c r="D205" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206">
+        <v>198</v>
+      </c>
+      <c r="B206">
+        <v>316522</v>
+      </c>
+      <c r="C206">
+        <v>158.261</v>
+      </c>
+      <c r="D206" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207">
+        <v>199</v>
+      </c>
+      <c r="B207">
+        <v>318102</v>
+      </c>
+      <c r="C207">
+        <v>159.051</v>
+      </c>
+      <c r="D207" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208">
+        <v>200</v>
+      </c>
+      <c r="B208">
+        <v>319692</v>
+      </c>
+      <c r="C208">
+        <v>159.846</v>
+      </c>
+      <c r="D208" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209">
+        <v>201</v>
+      </c>
+      <c r="B209">
+        <v>321373</v>
+      </c>
+      <c r="C209">
+        <v>160.687</v>
+      </c>
+      <c r="D209" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210">
+        <v>202</v>
+      </c>
+      <c r="B210">
+        <v>323022</v>
+      </c>
+      <c r="C210">
+        <v>161.511</v>
+      </c>
+      <c r="D210" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211">
+        <v>203</v>
+      </c>
+      <c r="B211">
+        <v>324722</v>
+      </c>
+      <c r="C211">
+        <v>162.361</v>
+      </c>
+      <c r="D211" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212">
+        <v>204</v>
+      </c>
+      <c r="B212">
+        <v>326382</v>
+      </c>
+      <c r="C212">
+        <v>163.191</v>
+      </c>
+      <c r="D212" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213">
+        <v>205</v>
+      </c>
+      <c r="B213">
+        <v>328012</v>
+      </c>
+      <c r="C213">
+        <v>164.006</v>
+      </c>
+      <c r="D213" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214">
+        <v>206</v>
+      </c>
+      <c r="B214">
+        <v>329622</v>
+      </c>
+      <c r="C214">
+        <v>164.811</v>
+      </c>
+      <c r="D214" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215">
+        <v>207</v>
+      </c>
+      <c r="B215">
+        <v>331192</v>
+      </c>
+      <c r="C215">
+        <v>165.596</v>
+      </c>
+      <c r="D215" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216">
+        <v>208</v>
+      </c>
+      <c r="B216">
+        <v>332682</v>
+      </c>
+      <c r="C216">
+        <v>166.341</v>
+      </c>
+      <c r="D216" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217">
+        <v>209</v>
+      </c>
+      <c r="B217">
+        <v>334182</v>
+      </c>
+      <c r="C217">
+        <v>167.091</v>
+      </c>
+      <c r="D217" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218">
+        <v>210</v>
+      </c>
+      <c r="B218">
+        <v>335782</v>
+      </c>
+      <c r="C218">
+        <v>167.891</v>
+      </c>
+      <c r="D218" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219">
+        <v>211</v>
+      </c>
+      <c r="B219">
+        <v>337382</v>
+      </c>
+      <c r="C219">
+        <v>168.691</v>
+      </c>
+      <c r="D219" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220">
+        <v>212</v>
+      </c>
+      <c r="B220">
+        <v>339042</v>
+      </c>
+      <c r="C220">
+        <v>169.521</v>
+      </c>
+      <c r="D220" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221">
+        <v>213</v>
+      </c>
+      <c r="B221">
+        <v>340742</v>
+      </c>
+      <c r="C221">
+        <v>170.371</v>
+      </c>
+      <c r="D221" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222">
+        <v>214</v>
+      </c>
+      <c r="B222">
+        <v>342372</v>
+      </c>
+      <c r="C222">
+        <v>171.186</v>
+      </c>
+      <c r="D222" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223">
+        <v>215</v>
+      </c>
+      <c r="B223">
+        <v>343950</v>
+      </c>
+      <c r="C223">
+        <v>171.975</v>
+      </c>
+      <c r="D223" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224">
+        <v>216</v>
+      </c>
+      <c r="B224">
+        <v>345540</v>
+      </c>
+      <c r="C224">
+        <v>172.77</v>
+      </c>
+      <c r="D224" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225">
+        <v>217</v>
+      </c>
+      <c r="B225">
+        <v>347090</v>
+      </c>
+      <c r="C225">
+        <v>173.545</v>
+      </c>
+      <c r="D225" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226">
+        <v>218</v>
+      </c>
+      <c r="B226">
+        <v>348600</v>
+      </c>
+      <c r="C226">
+        <v>174.3</v>
+      </c>
+      <c r="D226" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227">
+        <v>219</v>
+      </c>
+      <c r="B227">
+        <v>350130</v>
+      </c>
+      <c r="C227">
+        <v>175.065</v>
+      </c>
+      <c r="D227" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228">
+        <v>220</v>
+      </c>
+      <c r="B228">
+        <v>351670</v>
+      </c>
+      <c r="C228">
+        <v>175.835</v>
+      </c>
+      <c r="D228" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229">
+        <v>221</v>
+      </c>
+      <c r="B229">
+        <v>353240</v>
+      </c>
+      <c r="C229">
+        <v>176.62</v>
+      </c>
+      <c r="D229" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230">
+        <v>222</v>
+      </c>
+      <c r="B230">
+        <v>354880</v>
+      </c>
+      <c r="C230">
+        <v>177.44</v>
+      </c>
+      <c r="D230" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231">
+        <v>223</v>
+      </c>
+      <c r="B231">
+        <v>356530</v>
+      </c>
+      <c r="C231">
+        <v>178.265</v>
+      </c>
+      <c r="D231" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232">
+        <v>224</v>
+      </c>
+      <c r="B232">
+        <v>358170</v>
+      </c>
+      <c r="C232">
+        <v>179.085</v>
+      </c>
+      <c r="D232" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233">
+        <v>225</v>
+      </c>
+      <c r="B233">
+        <v>359830</v>
+      </c>
+      <c r="C233">
+        <v>179.915</v>
+      </c>
+      <c r="D233" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234">
+        <v>226</v>
+      </c>
+      <c r="B234">
+        <v>361440</v>
+      </c>
+      <c r="C234">
+        <v>180.72</v>
+      </c>
+      <c r="D234" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235">
+        <v>227</v>
+      </c>
+      <c r="B235">
+        <v>363010</v>
+      </c>
+      <c r="C235">
+        <v>181.505</v>
+      </c>
+      <c r="D235" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236">
+        <v>228</v>
+      </c>
+      <c r="B236">
+        <v>364510</v>
+      </c>
+      <c r="C236">
+        <v>182.255</v>
+      </c>
+      <c r="D236" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237">
+        <v>229</v>
+      </c>
+      <c r="B237">
+        <v>366020</v>
+      </c>
+      <c r="C237">
+        <v>183.01</v>
+      </c>
+      <c r="D237" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238">
+        <v>230</v>
+      </c>
+      <c r="B238">
+        <v>367540</v>
+      </c>
+      <c r="C238">
+        <v>183.77</v>
+      </c>
+      <c r="D238" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239">
+        <v>231</v>
+      </c>
+      <c r="B239">
+        <v>369100</v>
+      </c>
+      <c r="C239">
+        <v>184.55</v>
+      </c>
+      <c r="D239" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240">
+        <v>232</v>
+      </c>
+      <c r="B240">
+        <v>370730</v>
+      </c>
+      <c r="C240">
+        <v>185.365</v>
+      </c>
+      <c r="D240" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241">
+        <v>233</v>
+      </c>
+      <c r="B241">
+        <v>372380</v>
+      </c>
+      <c r="C241">
+        <v>186.19</v>
+      </c>
+      <c r="D241" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242">
+        <v>234</v>
+      </c>
+      <c r="B242">
+        <v>374070</v>
+      </c>
+      <c r="C242">
+        <v>187.035</v>
+      </c>
+      <c r="D242" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243">
+        <v>235</v>
+      </c>
+      <c r="B243">
+        <v>375740</v>
+      </c>
+      <c r="C243">
+        <v>187.87</v>
+      </c>
+      <c r="D243" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244">
+        <v>236</v>
+      </c>
+      <c r="B244">
+        <v>377420</v>
+      </c>
+      <c r="C244">
+        <v>188.71</v>
+      </c>
+      <c r="D244" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245">
+        <v>237</v>
+      </c>
+      <c r="B245">
+        <v>378970</v>
+      </c>
+      <c r="C245">
+        <v>189.485</v>
+      </c>
+      <c r="D245" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246">
+        <v>238</v>
+      </c>
+      <c r="B246">
+        <v>380530</v>
+      </c>
+      <c r="C246">
+        <v>190.265</v>
+      </c>
+      <c r="D246" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247">
+        <v>239</v>
+      </c>
+      <c r="B247">
+        <v>382050</v>
+      </c>
+      <c r="C247">
+        <v>191.025</v>
+      </c>
+      <c r="D247" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248">
+        <v>240</v>
+      </c>
+      <c r="B248">
+        <v>383571</v>
+      </c>
+      <c r="C248">
+        <v>191.786</v>
+      </c>
+      <c r="D248" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249">
+        <v>241</v>
+      </c>
+      <c r="B249">
+        <v>385100</v>
+      </c>
+      <c r="C249">
+        <v>192.55</v>
+      </c>
+      <c r="D249" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250">
+        <v>242</v>
+      </c>
+      <c r="B250">
+        <v>386700</v>
+      </c>
+      <c r="C250">
+        <v>193.35</v>
+      </c>
+      <c r="D250" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251">
+        <v>243</v>
+      </c>
+      <c r="B251">
+        <v>388370</v>
+      </c>
+      <c r="C251">
+        <v>194.185</v>
+      </c>
+      <c r="D251" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252">
+        <v>244</v>
+      </c>
+      <c r="B252">
+        <v>390040</v>
+      </c>
+      <c r="C252">
+        <v>195.02</v>
+      </c>
+      <c r="D252" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253">
+        <v>245</v>
+      </c>
+      <c r="B253">
+        <v>391720</v>
+      </c>
+      <c r="C253">
+        <v>195.86</v>
+      </c>
+      <c r="D253" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254">
+        <v>246</v>
+      </c>
+      <c r="B254">
+        <v>393360</v>
+      </c>
+      <c r="C254">
+        <v>196.68</v>
+      </c>
+      <c r="D254" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255">
+        <v>247</v>
+      </c>
+      <c r="B255">
+        <v>394990</v>
+      </c>
+      <c r="C255">
+        <v>197.495</v>
+      </c>
+      <c r="D255" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256">
+        <v>248</v>
+      </c>
+      <c r="B256">
+        <v>396550</v>
+      </c>
+      <c r="C256">
+        <v>198.275</v>
+      </c>
+      <c r="D256" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257">
+        <v>249</v>
+      </c>
+      <c r="B257">
+        <v>398020</v>
+      </c>
+      <c r="C257">
+        <v>199.01</v>
+      </c>
+      <c r="D257" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258">
+        <v>250</v>
+      </c>
+      <c r="B258">
+        <v>399530</v>
+      </c>
+      <c r="C258">
+        <v>199.765</v>
+      </c>
+      <c r="D258" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259">
+        <v>251</v>
+      </c>
+      <c r="B259">
+        <v>401020</v>
+      </c>
+      <c r="C259">
+        <v>200.51</v>
+      </c>
+      <c r="D259" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260">
+        <v>252</v>
+      </c>
+      <c r="B260">
+        <v>402530</v>
+      </c>
+      <c r="C260">
+        <v>201.265</v>
+      </c>
+      <c r="D260" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261">
+        <v>253</v>
+      </c>
+      <c r="B261">
+        <v>404150</v>
+      </c>
+      <c r="C261">
+        <v>202.075</v>
+      </c>
+      <c r="D261" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262">
+        <v>254</v>
+      </c>
+      <c r="B262">
+        <v>405850</v>
+      </c>
+      <c r="C262">
+        <v>202.925</v>
+      </c>
+      <c r="D262" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263">
+        <v>255</v>
+      </c>
+      <c r="B263">
+        <v>407530</v>
+      </c>
+      <c r="C263">
+        <v>203.765</v>
+      </c>
+      <c r="D263" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264">
+        <v>256</v>
+      </c>
+      <c r="B264">
+        <v>409170</v>
+      </c>
+      <c r="C264">
+        <v>204.585</v>
+      </c>
+      <c r="D264" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265">
+        <v>257</v>
+      </c>
+      <c r="B265">
+        <v>410770</v>
+      </c>
+      <c r="C265">
+        <v>205.385</v>
+      </c>
+      <c r="D265" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266">
+        <v>258</v>
+      </c>
+      <c r="B266">
+        <v>412380</v>
+      </c>
+      <c r="C266">
+        <v>206.19</v>
+      </c>
+      <c r="D266" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267">
+        <v>259</v>
+      </c>
+      <c r="B267">
+        <v>413920</v>
+      </c>
+      <c r="C267">
+        <v>206.96</v>
+      </c>
+      <c r="D267" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268">
+        <v>260</v>
+      </c>
+      <c r="B268">
+        <v>415440</v>
+      </c>
+      <c r="C268">
+        <v>207.72</v>
+      </c>
+      <c r="D268" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269">
+        <v>261</v>
+      </c>
+      <c r="B269">
+        <v>416970</v>
+      </c>
+      <c r="C269">
+        <v>208.485</v>
+      </c>
+      <c r="D269" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270">
+        <v>262</v>
+      </c>
+      <c r="B270">
+        <v>418530</v>
+      </c>
+      <c r="C270">
+        <v>209.265</v>
+      </c>
+      <c r="D270" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271">
+        <v>263</v>
+      </c>
+      <c r="B271">
+        <v>420160</v>
+      </c>
+      <c r="C271">
+        <v>210.08</v>
+      </c>
+      <c r="D271" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272">
+        <v>264</v>
+      </c>
+      <c r="B272">
+        <v>421830</v>
+      </c>
+      <c r="C272">
+        <v>210.915</v>
+      </c>
+      <c r="D272" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273">
+        <v>265</v>
+      </c>
+      <c r="B273">
+        <v>423510</v>
+      </c>
+      <c r="C273">
+        <v>211.755</v>
+      </c>
+      <c r="D273" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274">
+        <v>266</v>
+      </c>
+      <c r="B274">
+        <v>425160</v>
+      </c>
+      <c r="C274">
+        <v>212.58</v>
+      </c>
+      <c r="D274" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275">
+        <v>267</v>
+      </c>
+      <c r="B275">
+        <v>426820</v>
+      </c>
+      <c r="C275">
+        <v>213.41</v>
+      </c>
+      <c r="D275" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276">
+        <v>268</v>
+      </c>
+      <c r="B276">
+        <v>428410</v>
+      </c>
+      <c r="C276">
+        <v>214.205</v>
+      </c>
+      <c r="D276" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277">
+        <v>269</v>
+      </c>
+      <c r="B277">
+        <v>429982</v>
+      </c>
+      <c r="C277">
+        <v>214.991</v>
+      </c>
+      <c r="D277" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278">
+        <v>270</v>
+      </c>
+      <c r="B278">
+        <v>431473</v>
+      </c>
+      <c r="C278">
+        <v>215.737</v>
+      </c>
+      <c r="D278" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279">
+        <v>271</v>
+      </c>
+      <c r="B279">
+        <v>432992</v>
+      </c>
+      <c r="C279">
+        <v>216.496</v>
+      </c>
+      <c r="D279" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280">
+        <v>272</v>
+      </c>
+      <c r="B280">
+        <v>434542</v>
+      </c>
+      <c r="C280">
+        <v>217.271</v>
+      </c>
+      <c r="D280" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281">
+        <v>273</v>
+      </c>
+      <c r="B281">
+        <v>436092</v>
+      </c>
+      <c r="C281">
+        <v>218.046</v>
+      </c>
+      <c r="D281" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282">
+        <v>274</v>
+      </c>
+      <c r="B282">
+        <v>437772</v>
+      </c>
+      <c r="C282">
+        <v>218.886</v>
+      </c>
+      <c r="D282" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283">
+        <v>275</v>
+      </c>
+      <c r="B283">
+        <v>439472</v>
+      </c>
+      <c r="C283">
+        <v>219.736</v>
+      </c>
+      <c r="D283" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284">
+        <v>276</v>
+      </c>
+      <c r="B284">
+        <v>441142</v>
+      </c>
+      <c r="C284">
+        <v>220.571</v>
+      </c>
+      <c r="D284" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285">
+        <v>277</v>
+      </c>
+      <c r="B285">
+        <v>442822</v>
+      </c>
+      <c r="C285">
+        <v>221.411</v>
+      </c>
+      <c r="D285" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286">
+        <v>278</v>
+      </c>
+      <c r="B286">
+        <v>444453</v>
+      </c>
+      <c r="C286">
+        <v>222.227</v>
+      </c>
+      <c r="D286" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287">
+        <v>279</v>
+      </c>
+      <c r="B287">
+        <v>445972</v>
+      </c>
+      <c r="C287">
+        <v>222.986</v>
+      </c>
+      <c r="D287" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288">
+        <v>280</v>
+      </c>
+      <c r="B288">
+        <v>447512</v>
+      </c>
+      <c r="C288">
+        <v>223.756</v>
+      </c>
+      <c r="D288" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289">
+        <v>281</v>
+      </c>
+      <c r="B289">
+        <v>449032</v>
+      </c>
+      <c r="C289">
+        <v>224.516</v>
+      </c>
+      <c r="D289" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290">
+        <v>282</v>
+      </c>
+      <c r="B290">
+        <v>450563</v>
+      </c>
+      <c r="C290">
+        <v>225.282</v>
+      </c>
+      <c r="D290" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291">
+        <v>283</v>
+      </c>
+      <c r="B291">
+        <v>452103</v>
+      </c>
+      <c r="C291">
+        <v>226.052</v>
+      </c>
+      <c r="D291" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292">
+        <v>284</v>
+      </c>
+      <c r="B292">
+        <v>453712</v>
+      </c>
+      <c r="C292">
+        <v>226.856</v>
+      </c>
+      <c r="D292" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293">
+        <v>285</v>
+      </c>
+      <c r="B293">
+        <v>455362</v>
+      </c>
+      <c r="C293">
+        <v>227.681</v>
+      </c>
+      <c r="D293" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294">
+        <v>286</v>
+      </c>
+      <c r="B294">
+        <v>457072</v>
+      </c>
+      <c r="C294">
+        <v>228.536</v>
+      </c>
+      <c r="D294" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295">
+        <v>287</v>
+      </c>
+      <c r="B295">
+        <v>458752</v>
+      </c>
+      <c r="C295">
+        <v>229.376</v>
+      </c>
+      <c r="D295" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296">
+        <v>288</v>
+      </c>
+      <c r="B296">
+        <v>460392</v>
+      </c>
+      <c r="C296">
+        <v>230.196</v>
+      </c>
+      <c r="D296" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297">
+        <v>289</v>
+      </c>
+      <c r="B297">
+        <v>462032</v>
+      </c>
+      <c r="C297">
+        <v>231.016</v>
+      </c>
+      <c r="D297" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298">
+        <v>290</v>
+      </c>
+      <c r="B298">
+        <v>463572</v>
+      </c>
+      <c r="C298">
+        <v>231.786</v>
+      </c>
+      <c r="D298" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299">
+        <v>291</v>
+      </c>
+      <c r="B299">
+        <v>465083</v>
+      </c>
+      <c r="C299">
+        <v>232.542</v>
+      </c>
+      <c r="D299" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300">
+        <v>292</v>
+      </c>
+      <c r="B300">
+        <v>466563</v>
+      </c>
+      <c r="C300">
+        <v>233.282</v>
+      </c>
+      <c r="D300" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301">
+        <v>293</v>
+      </c>
+      <c r="B301">
+        <v>468152</v>
+      </c>
+      <c r="C301">
+        <v>234.076</v>
+      </c>
+      <c r="D301" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302">
+        <v>294</v>
+      </c>
+      <c r="B302">
+        <v>469762</v>
+      </c>
+      <c r="C302">
+        <v>234.881</v>
+      </c>
+      <c r="D302" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303">
+        <v>295</v>
+      </c>
+      <c r="B303">
+        <v>471422</v>
+      </c>
+      <c r="C303">
+        <v>235.711</v>
+      </c>
+      <c r="D303" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304">
+        <v>296</v>
+      </c>
+      <c r="B304">
+        <v>473106</v>
+      </c>
+      <c r="C304">
+        <v>236.553</v>
+      </c>
+      <c r="D304" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305">
+        <v>297</v>
+      </c>
+      <c r="B305">
+        <v>474786</v>
+      </c>
+      <c r="C305">
+        <v>237.393</v>
+      </c>
+      <c r="D305" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306">
+        <v>298</v>
+      </c>
+      <c r="B306">
+        <v>476447</v>
+      </c>
+      <c r="C306">
+        <v>238.224</v>
+      </c>
+      <c r="D306" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307">
+        <v>299</v>
+      </c>
+      <c r="B307">
+        <v>478067</v>
+      </c>
+      <c r="C307">
+        <v>239.034</v>
+      </c>
+      <c r="D307" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308">
+        <v>300</v>
+      </c>
+      <c r="B308">
+        <v>479636</v>
+      </c>
+      <c r="C308">
+        <v>239.818</v>
+      </c>
+      <c r="D308" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309">
+        <v>301</v>
+      </c>
+      <c r="B309">
+        <v>481176</v>
+      </c>
+      <c r="C309">
+        <v>240.588</v>
+      </c>
+      <c r="D309" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310">
+        <v>302</v>
+      </c>
+      <c r="B310">
+        <v>482727</v>
+      </c>
+      <c r="C310">
+        <v>241.364</v>
+      </c>
+      <c r="D310" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311">
+        <v>303</v>
+      </c>
+      <c r="B311">
+        <v>484276</v>
+      </c>
+      <c r="C311">
+        <v>242.138</v>
+      </c>
+      <c r="D311" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312">
+        <v>304</v>
+      </c>
+      <c r="B312">
+        <v>485837</v>
+      </c>
+      <c r="C312">
+        <v>242.919</v>
+      </c>
+      <c r="D312" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313">
+        <v>305</v>
+      </c>
+      <c r="B313">
+        <v>487437</v>
+      </c>
+      <c r="C313">
+        <v>243.719</v>
+      </c>
+      <c r="D313" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314">
+        <v>306</v>
+      </c>
+      <c r="B314">
+        <v>489086</v>
+      </c>
+      <c r="C314">
+        <v>244.543</v>
+      </c>
+      <c r="D314" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315">
+        <v>307</v>
+      </c>
+      <c r="B315">
+        <v>490797</v>
+      </c>
+      <c r="C315">
+        <v>245.399</v>
+      </c>
+      <c r="D315" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316">
+        <v>308</v>
+      </c>
+      <c r="B316">
+        <v>492487</v>
+      </c>
+      <c r="C316">
+        <v>246.244</v>
+      </c>
+      <c r="D316" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317">
+        <v>309</v>
+      </c>
+      <c r="B317">
+        <v>494127</v>
+      </c>
+      <c r="C317">
+        <v>247.064</v>
+      </c>
+      <c r="D317" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318">
+        <v>310</v>
+      </c>
+      <c r="B318">
+        <v>495717</v>
+      </c>
+      <c r="C318">
+        <v>247.859</v>
+      </c>
+      <c r="D318" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319">
+        <v>311</v>
+      </c>
+      <c r="B319">
+        <v>497246</v>
+      </c>
+      <c r="C319">
+        <v>248.623</v>
+      </c>
+      <c r="D319" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320">
+        <v>312</v>
+      </c>
+      <c r="B320">
+        <v>498766</v>
+      </c>
+      <c r="C320">
+        <v>249.383</v>
+      </c>
+      <c r="D320" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321">
+        <v>313</v>
+      </c>
+      <c r="B321">
+        <v>500307</v>
+      </c>
+      <c r="C321">
+        <v>250.154</v>
+      </c>
+      <c r="D321" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322">
+        <v>314</v>
+      </c>
+      <c r="B322">
+        <v>501847</v>
+      </c>
+      <c r="C322">
+        <v>250.924</v>
+      </c>
+      <c r="D322" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323">
+        <v>315</v>
+      </c>
+      <c r="B323">
+        <v>503436</v>
+      </c>
+      <c r="C323">
+        <v>251.718</v>
+      </c>
+      <c r="D323" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324">
+        <v>316</v>
+      </c>
+      <c r="B324">
+        <v>505067</v>
+      </c>
+      <c r="C324">
+        <v>252.534</v>
+      </c>
+      <c r="D324" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325">
+        <v>317</v>
+      </c>
+      <c r="B325">
+        <v>506746</v>
+      </c>
+      <c r="C325">
+        <v>253.373</v>
+      </c>
+      <c r="D325" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326">
+        <v>318</v>
+      </c>
+      <c r="B326">
+        <v>508386</v>
+      </c>
+      <c r="C326">
+        <v>254.193</v>
+      </c>
+      <c r="D326" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327">
+        <v>319</v>
+      </c>
+      <c r="B327">
+        <v>510037</v>
+      </c>
+      <c r="C327">
+        <v>255.019</v>
+      </c>
+      <c r="D327" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328">
+        <v>320</v>
+      </c>
+      <c r="B328">
+        <v>511637</v>
+      </c>
+      <c r="C328">
+        <v>255.819</v>
+      </c>
+      <c r="D328" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329">
+        <v>321</v>
+      </c>
+      <c r="B329">
+        <v>513227</v>
+      </c>
+      <c r="C329">
+        <v>256.614</v>
+      </c>
+      <c r="D329" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330">
+        <v>322</v>
+      </c>
+      <c r="B330">
+        <v>514743</v>
+      </c>
+      <c r="C330">
+        <v>257.372</v>
+      </c>
+      <c r="D330" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331">
+        <v>323</v>
+      </c>
+      <c r="B331">
+        <v>516273</v>
+      </c>
+      <c r="C331">
+        <v>258.137</v>
+      </c>
+      <c r="D331" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332">
+        <v>324</v>
+      </c>
+      <c r="B332">
+        <v>517843</v>
+      </c>
+      <c r="C332">
+        <v>258.921</v>
+      </c>
+      <c r="D332" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333">
+        <v>325</v>
+      </c>
+      <c r="B333">
+        <v>519404</v>
+      </c>
+      <c r="C333">
+        <v>259.702</v>
+      </c>
+      <c r="D333" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334">
+        <v>326</v>
+      </c>
+      <c r="B334">
+        <v>521013</v>
+      </c>
+      <c r="C334">
+        <v>260.507</v>
+      </c>
+      <c r="D334" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335">
+        <v>327</v>
+      </c>
+      <c r="B335">
+        <v>522673</v>
+      </c>
+      <c r="C335">
+        <v>261.337</v>
+      </c>
+      <c r="D335" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336">
+        <v>328</v>
+      </c>
+      <c r="B336">
+        <v>524353</v>
+      </c>
+      <c r="C336">
+        <v>262.177</v>
+      </c>
+      <c r="D336" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337">
+        <v>329</v>
+      </c>
+      <c r="B337">
+        <v>526003</v>
+      </c>
+      <c r="C337">
+        <v>263.002</v>
+      </c>
+      <c r="D337" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338">
+        <v>330</v>
+      </c>
+      <c r="B338">
+        <v>527653</v>
+      </c>
+      <c r="C338">
+        <v>263.827</v>
+      </c>
+      <c r="D338" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339">
+        <v>331</v>
+      </c>
+      <c r="B339">
+        <v>529293</v>
+      </c>
+      <c r="C339">
+        <v>264.647</v>
+      </c>
+      <c r="D339" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340">
+        <v>332</v>
+      </c>
+      <c r="B340">
+        <v>530834</v>
+      </c>
+      <c r="C340">
+        <v>265.417</v>
+      </c>
+      <c r="D340" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341">
+        <v>333</v>
+      </c>
+      <c r="B341">
+        <v>532354</v>
+      </c>
+      <c r="C341">
+        <v>266.177</v>
+      </c>
+      <c r="D341" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342">
+        <v>334</v>
+      </c>
+      <c r="B342">
+        <v>533853</v>
+      </c>
+      <c r="C342">
+        <v>266.927</v>
+      </c>
+      <c r="D342" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343">
+        <v>335</v>
+      </c>
+      <c r="B343">
+        <v>535413</v>
+      </c>
+      <c r="C343">
+        <v>267.707</v>
+      </c>
+      <c r="D343" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344">
+        <v>336</v>
+      </c>
+      <c r="B344">
+        <v>536974</v>
+      </c>
+      <c r="C344">
+        <v>268.487</v>
+      </c>
+      <c r="D344" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345">
+        <v>337</v>
+      </c>
+      <c r="B345">
+        <v>538593</v>
+      </c>
+      <c r="C345">
+        <v>269.297</v>
+      </c>
+      <c r="D345" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346">
+        <v>338</v>
+      </c>
+      <c r="B346">
+        <v>540294</v>
+      </c>
+      <c r="C346">
+        <v>270.147</v>
+      </c>
+      <c r="D346" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347">
+        <v>339</v>
+      </c>
+      <c r="B347">
+        <v>541953</v>
+      </c>
+      <c r="C347">
+        <v>270.977</v>
+      </c>
+      <c r="D347" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348">
+        <v>340</v>
+      </c>
+      <c r="B348">
+        <v>543634</v>
+      </c>
+      <c r="C348">
+        <v>271.817</v>
+      </c>
+      <c r="D348" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349">
+        <v>341</v>
+      </c>
+      <c r="B349">
+        <v>545293</v>
+      </c>
+      <c r="C349">
+        <v>272.647</v>
+      </c>
+      <c r="D349" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350">
+        <v>342</v>
+      </c>
+      <c r="B350">
+        <v>546863</v>
+      </c>
+      <c r="C350">
+        <v>273.432</v>
+      </c>
+      <c r="D350" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351">
+        <v>343</v>
+      </c>
+      <c r="B351">
+        <v>548413</v>
+      </c>
+      <c r="C351">
+        <v>274.207</v>
+      </c>
+      <c r="D351" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352">
+        <v>344</v>
+      </c>
+      <c r="B352">
+        <v>549974</v>
+      </c>
+      <c r="C352">
+        <v>274.987</v>
+      </c>
+      <c r="D352" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353">
+        <v>345</v>
+      </c>
+      <c r="B353">
+        <v>551513</v>
+      </c>
+      <c r="C353">
+        <v>275.757</v>
+      </c>
+      <c r="D353" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354">
+        <v>346</v>
+      </c>
+      <c r="B354">
+        <v>553064</v>
+      </c>
+      <c r="C354">
+        <v>276.532</v>
+      </c>
+      <c r="D354" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355">
+        <v>347</v>
+      </c>
+      <c r="B355">
+        <v>554653</v>
+      </c>
+      <c r="C355">
+        <v>277.327</v>
+      </c>
+      <c r="D355" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356">
+        <v>348</v>
+      </c>
+      <c r="B356">
+        <v>556314</v>
+      </c>
+      <c r="C356">
+        <v>278.157</v>
+      </c>
+      <c r="D356" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357">
+        <v>349</v>
+      </c>
+      <c r="B357">
+        <v>558032</v>
+      </c>
+      <c r="C357">
+        <v>279.016</v>
+      </c>
+      <c r="D357" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358">
+        <v>350</v>
+      </c>
+      <c r="B358">
+        <v>559722</v>
+      </c>
+      <c r="C358">
+        <v>279.861</v>
+      </c>
+      <c r="D358" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359">
+        <v>351</v>
+      </c>
+      <c r="B359">
+        <v>561342</v>
+      </c>
+      <c r="C359">
+        <v>280.671</v>
+      </c>
+      <c r="D359" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360">
+        <v>352</v>
+      </c>
+      <c r="B360">
+        <v>562912</v>
+      </c>
+      <c r="C360">
+        <v>281.456</v>
+      </c>
+      <c r="D360" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361">
+        <v>353</v>
+      </c>
+      <c r="B361">
+        <v>564442</v>
+      </c>
+      <c r="C361">
+        <v>282.221</v>
+      </c>
+      <c r="D361" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362">
+        <v>354</v>
+      </c>
+      <c r="B362">
+        <v>565972</v>
+      </c>
+      <c r="C362">
+        <v>282.986</v>
+      </c>
+      <c r="D362" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363">
+        <v>355</v>
+      </c>
+      <c r="B363">
+        <v>567492</v>
+      </c>
+      <c r="C363">
+        <v>283.746</v>
+      </c>
+      <c r="D363" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364">
+        <v>356</v>
+      </c>
+      <c r="B364">
+        <v>569052</v>
+      </c>
+      <c r="C364">
+        <v>284.526</v>
+      </c>
+      <c r="D364" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365">
+        <v>357</v>
+      </c>
+      <c r="B365">
+        <v>570653</v>
+      </c>
+      <c r="C365">
+        <v>285.327</v>
+      </c>
+      <c r="D365" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366">
+        <v>358</v>
+      </c>
+      <c r="B366">
+        <v>572292</v>
+      </c>
+      <c r="C366">
+        <v>286.146</v>
+      </c>
+      <c r="D366" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367">
+        <v>359</v>
+      </c>
+      <c r="B367">
+        <v>573963</v>
+      </c>
+      <c r="C367">
+        <v>286.982</v>
+      </c>
+      <c r="D367" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368">
+        <v>360</v>
+      </c>
+      <c r="B368">
+        <v>575652</v>
+      </c>
+      <c r="C368">
+        <v>287.826</v>
+      </c>
+      <c r="D368" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369">
+        <v>361</v>
+      </c>
+      <c r="B369">
+        <v>577302</v>
+      </c>
+      <c r="C369">
+        <v>288.651</v>
+      </c>
+      <c r="D369" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370">
+        <v>362</v>
+      </c>
+      <c r="B370">
+        <v>578932</v>
+      </c>
+      <c r="C370">
+        <v>289.466</v>
+      </c>
+      <c r="D370" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371">
+        <v>363</v>
+      </c>
+      <c r="B371">
+        <v>580542</v>
+      </c>
+      <c r="C371">
+        <v>290.271</v>
+      </c>
+      <c r="D371" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372">
+        <v>364</v>
+      </c>
+      <c r="B372">
+        <v>582083</v>
+      </c>
+      <c r="C372">
+        <v>291.042</v>
+      </c>
+      <c r="D372" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373">
+        <v>365</v>
+      </c>
+      <c r="B373">
+        <v>583603</v>
+      </c>
+      <c r="C373">
+        <v>291.802</v>
+      </c>
+      <c r="D373" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374">
+        <v>366</v>
+      </c>
+      <c r="B374">
+        <v>585102</v>
+      </c>
+      <c r="C374">
+        <v>292.551</v>
+      </c>
+      <c r="D374" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375">
+        <v>367</v>
+      </c>
+      <c r="B375">
+        <v>586692</v>
+      </c>
+      <c r="C375">
+        <v>293.346</v>
+      </c>
+      <c r="D375" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376">
+        <v>368</v>
+      </c>
+      <c r="B376">
+        <v>588262</v>
+      </c>
+      <c r="C376">
+        <v>294.131</v>
+      </c>
+      <c r="D376" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377">
+        <v>369</v>
+      </c>
+      <c r="B377">
+        <v>589892</v>
+      </c>
+      <c r="C377">
+        <v>294.946</v>
+      </c>
+      <c r="D377" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378">
+        <v>370</v>
+      </c>
+      <c r="B378">
+        <v>591592</v>
+      </c>
+      <c r="C378">
+        <v>295.796</v>
+      </c>
+      <c r="D378" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379">
+        <v>371</v>
+      </c>
+      <c r="B379">
+        <v>593282</v>
+      </c>
+      <c r="C379">
+        <v>296.641</v>
+      </c>
+      <c r="D379" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380">
+        <v>372</v>
+      </c>
+      <c r="B380">
+        <v>594912</v>
+      </c>
+      <c r="C380">
+        <v>297.456</v>
+      </c>
+      <c r="D380" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381">
+        <v>373</v>
+      </c>
+      <c r="B381">
+        <v>596462</v>
+      </c>
+      <c r="C381">
+        <v>298.231</v>
+      </c>
+      <c r="D381" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382">
+        <v>374</v>
+      </c>
+      <c r="B382">
+        <v>597992</v>
+      </c>
+      <c r="C382">
+        <v>298.996</v>
+      </c>
+      <c r="D382" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383">
+        <v>375</v>
+      </c>
+      <c r="B383">
+        <v>599502</v>
+      </c>
+      <c r="C383">
+        <v>299.751</v>
+      </c>
+      <c r="D383" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:D383"/>
+  </ignoredErrors>
+</worksheet>
 </file>
--- a/EXAMPLE/synthetic_ecg_5min.xlsx
+++ b/EXAMPLE/synthetic_ecg_5min.xlsx
@@ -4539,9 +4539,9 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D383"/>
+  <dimension ref="A1:D385"/>
   <cols>
-    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
     <col min="3" max="3" width="10.83203125" customWidth="1"/>
     <col min="4" max="4" width="8.83203125" customWidth="1"/>
@@ -4562,7 +4562,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>date</v>
+        <v>date_of_ecg</v>
       </c>
       <c r="B3" t="str">
         <v>2016-10-16</v>
@@ -4570,79 +4570,67 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>sensitivity</v>
-      </c>
-      <c r="B4">
-        <v>5</v>
+        <v>ecg_filename</v>
+      </c>
+      <c r="B4" t="str">
+        <v>ZK-ECG000_2016_10_16.pdf</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>samples</v>
-      </c>
-      <c r="B5">
-        <v>600503</v>
+        <v>ecg_analysis_filename</v>
+      </c>
+      <c r="B5" t="str">
+        <v>ZK-ECG000_2016_10_16.xlsx</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>source_pdf</v>
-      </c>
-      <c r="B6" t="str">
-        <v>synthetic_ecg_5min</v>
+        <v>sensitivity</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>samples</v>
+      </c>
+      <c r="B7">
+        <v>600503</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
+        <v>source_pdf</v>
+      </c>
+      <c r="B8" t="str">
+        <v>synthetic_ecg_5min</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
         <v>beat</v>
       </c>
-      <c r="B8" t="str">
+      <c r="B10" t="str">
         <v>sample</v>
       </c>
-      <c r="C8" t="str">
+      <c r="C10" t="str">
         <v>time_s</v>
       </c>
-      <c r="D8" t="str">
+      <c r="D10" t="str">
         <v>tag</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9">
-        <v>1</v>
-      </c>
-      <c r="B9">
-        <v>2000</v>
-      </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9" t="str">
-        <v>Normal</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10">
-        <v>2</v>
-      </c>
-      <c r="B10">
-        <v>3640</v>
-      </c>
-      <c r="C10">
-        <v>1.82</v>
-      </c>
-      <c r="D10" t="str">
-        <v>Normal</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B11">
-        <v>5330</v>
+        <v>2000</v>
       </c>
       <c r="C11">
-        <v>2.665</v>
+        <v>1</v>
       </c>
       <c r="D11" t="str">
         <v>Normal</v>
@@ -4650,13 +4638,13 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B12">
-        <v>7000</v>
+        <v>3640</v>
       </c>
       <c r="C12">
-        <v>3.5</v>
+        <v>1.82</v>
       </c>
       <c r="D12" t="str">
         <v>Normal</v>
@@ -4664,13 +4652,13 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B13">
-        <v>8630</v>
+        <v>5330</v>
       </c>
       <c r="C13">
-        <v>4.315</v>
+        <v>2.665</v>
       </c>
       <c r="D13" t="str">
         <v>Normal</v>
@@ -4678,13 +4666,13 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B14">
-        <v>10230</v>
+        <v>7000</v>
       </c>
       <c r="C14">
-        <v>5.115</v>
+        <v>3.5</v>
       </c>
       <c r="D14" t="str">
         <v>Normal</v>
@@ -4692,13 +4680,13 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B15">
-        <v>11770</v>
+        <v>8630</v>
       </c>
       <c r="C15">
-        <v>5.885</v>
+        <v>4.315</v>
       </c>
       <c r="D15" t="str">
         <v>Normal</v>
@@ -4706,13 +4694,13 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B16">
-        <v>13300</v>
+        <v>10230</v>
       </c>
       <c r="C16">
-        <v>6.65</v>
+        <v>5.115</v>
       </c>
       <c r="D16" t="str">
         <v>Normal</v>
@@ -4720,13 +4708,13 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B17">
-        <v>14860</v>
+        <v>11770</v>
       </c>
       <c r="C17">
-        <v>7.43</v>
+        <v>5.885</v>
       </c>
       <c r="D17" t="str">
         <v>Normal</v>
@@ -4734,13 +4722,13 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B18">
-        <v>16380</v>
+        <v>13300</v>
       </c>
       <c r="C18">
-        <v>8.19</v>
+        <v>6.65</v>
       </c>
       <c r="D18" t="str">
         <v>Normal</v>
@@ -4748,13 +4736,13 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B19">
-        <v>17950</v>
+        <v>14860</v>
       </c>
       <c r="C19">
-        <v>8.975</v>
+        <v>7.43</v>
       </c>
       <c r="D19" t="str">
         <v>Normal</v>
@@ -4762,13 +4750,13 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B20">
-        <v>19580</v>
+        <v>16380</v>
       </c>
       <c r="C20">
-        <v>9.79</v>
+        <v>8.19</v>
       </c>
       <c r="D20" t="str">
         <v>Normal</v>
@@ -4776,13 +4764,13 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B21">
-        <v>21250</v>
+        <v>17950</v>
       </c>
       <c r="C21">
-        <v>10.625</v>
+        <v>8.975</v>
       </c>
       <c r="D21" t="str">
         <v>Normal</v>
@@ -4790,13 +4778,13 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B22">
-        <v>22940</v>
+        <v>19580</v>
       </c>
       <c r="C22">
-        <v>11.47</v>
+        <v>9.79</v>
       </c>
       <c r="D22" t="str">
         <v>Normal</v>
@@ -4804,13 +4792,13 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B23">
-        <v>24580</v>
+        <v>21250</v>
       </c>
       <c r="C23">
-        <v>12.29</v>
+        <v>10.625</v>
       </c>
       <c r="D23" t="str">
         <v>Normal</v>
@@ -4818,13 +4806,13 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B24">
-        <v>26210</v>
+        <v>22940</v>
       </c>
       <c r="C24">
-        <v>13.105</v>
+        <v>11.47</v>
       </c>
       <c r="D24" t="str">
         <v>Normal</v>
@@ -4832,13 +4820,13 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B25">
-        <v>27820</v>
+        <v>24580</v>
       </c>
       <c r="C25">
-        <v>13.91</v>
+        <v>12.29</v>
       </c>
       <c r="D25" t="str">
         <v>Normal</v>
@@ -4846,13 +4834,13 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B26">
-        <v>29330</v>
+        <v>26210</v>
       </c>
       <c r="C26">
-        <v>14.665</v>
+        <v>13.105</v>
       </c>
       <c r="D26" t="str">
         <v>Normal</v>
@@ -4860,13 +4848,13 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B27">
-        <v>30840</v>
+        <v>27820</v>
       </c>
       <c r="C27">
-        <v>15.42</v>
+        <v>13.91</v>
       </c>
       <c r="D27" t="str">
         <v>Normal</v>
@@ -4874,13 +4862,13 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B28">
-        <v>32320</v>
+        <v>29330</v>
       </c>
       <c r="C28">
-        <v>16.16</v>
+        <v>14.665</v>
       </c>
       <c r="D28" t="str">
         <v>Normal</v>
@@ -4888,13 +4876,13 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B29">
-        <v>33850</v>
+        <v>30840</v>
       </c>
       <c r="C29">
-        <v>16.925</v>
+        <v>15.42</v>
       </c>
       <c r="D29" t="str">
         <v>Normal</v>
@@ -4902,13 +4890,13 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B30">
-        <v>35410</v>
+        <v>32320</v>
       </c>
       <c r="C30">
-        <v>17.705</v>
+        <v>16.16</v>
       </c>
       <c r="D30" t="str">
         <v>Normal</v>
@@ -4916,13 +4904,13 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B31">
-        <v>37050</v>
+        <v>33850</v>
       </c>
       <c r="C31">
-        <v>18.525</v>
+        <v>16.925</v>
       </c>
       <c r="D31" t="str">
         <v>Normal</v>
@@ -4930,13 +4918,13 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B32">
-        <v>38690</v>
+        <v>35410</v>
       </c>
       <c r="C32">
-        <v>19.345</v>
+        <v>17.705</v>
       </c>
       <c r="D32" t="str">
         <v>Normal</v>
@@ -4944,13 +4932,13 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B33">
-        <v>40380</v>
+        <v>37050</v>
       </c>
       <c r="C33">
-        <v>20.19</v>
+        <v>18.525</v>
       </c>
       <c r="D33" t="str">
         <v>Normal</v>
@@ -4958,13 +4946,13 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B34">
-        <v>42030</v>
+        <v>38690</v>
       </c>
       <c r="C34">
-        <v>21.015</v>
+        <v>19.345</v>
       </c>
       <c r="D34" t="str">
         <v>Normal</v>
@@ -4972,13 +4960,13 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B35">
-        <v>43632</v>
+        <v>40380</v>
       </c>
       <c r="C35">
-        <v>21.816</v>
+        <v>20.19</v>
       </c>
       <c r="D35" t="str">
         <v>Normal</v>
@@ -4986,13 +4974,13 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B36">
-        <v>45132</v>
+        <v>42030</v>
       </c>
       <c r="C36">
-        <v>22.566</v>
+        <v>21.015</v>
       </c>
       <c r="D36" t="str">
         <v>Normal</v>
@@ -5000,13 +4988,13 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B37">
-        <v>46643</v>
+        <v>43632</v>
       </c>
       <c r="C37">
-        <v>23.322</v>
+        <v>21.816</v>
       </c>
       <c r="D37" t="str">
         <v>Normal</v>
@@ -5014,13 +5002,13 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B38">
-        <v>48163</v>
+        <v>45132</v>
       </c>
       <c r="C38">
-        <v>24.082</v>
+        <v>22.566</v>
       </c>
       <c r="D38" t="str">
         <v>Normal</v>
@@ -5028,13 +5016,13 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B39">
-        <v>49712</v>
+        <v>46643</v>
       </c>
       <c r="C39">
-        <v>24.856</v>
+        <v>23.322</v>
       </c>
       <c r="D39" t="str">
         <v>Normal</v>
@@ -5042,13 +5030,13 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B40">
-        <v>51252</v>
+        <v>48163</v>
       </c>
       <c r="C40">
-        <v>25.626</v>
+        <v>24.082</v>
       </c>
       <c r="D40" t="str">
         <v>Normal</v>
@@ -5056,13 +5044,13 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B41">
-        <v>52872</v>
+        <v>49712</v>
       </c>
       <c r="C41">
-        <v>26.436</v>
+        <v>24.856</v>
       </c>
       <c r="D41" t="str">
         <v>Normal</v>
@@ -5070,13 +5058,13 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B42">
-        <v>54512</v>
+        <v>51252</v>
       </c>
       <c r="C42">
-        <v>27.256</v>
+        <v>25.626</v>
       </c>
       <c r="D42" t="str">
         <v>Normal</v>
@@ -5084,13 +5072,13 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B43">
-        <v>56172</v>
+        <v>52872</v>
       </c>
       <c r="C43">
-        <v>28.086</v>
+        <v>26.436</v>
       </c>
       <c r="D43" t="str">
         <v>Normal</v>
@@ -5098,13 +5086,13 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B44">
-        <v>57862</v>
+        <v>54512</v>
       </c>
       <c r="C44">
-        <v>28.931</v>
+        <v>27.256</v>
       </c>
       <c r="D44" t="str">
         <v>Normal</v>
@@ -5112,13 +5100,13 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B45">
-        <v>59472</v>
+        <v>56172</v>
       </c>
       <c r="C45">
-        <v>29.736</v>
+        <v>28.086</v>
       </c>
       <c r="D45" t="str">
         <v>Normal</v>
@@ -5126,13 +5114,13 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B46">
-        <v>61053</v>
+        <v>57862</v>
       </c>
       <c r="C46">
-        <v>30.527</v>
+        <v>28.931</v>
       </c>
       <c r="D46" t="str">
         <v>Normal</v>
@@ -5140,13 +5128,13 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B47">
-        <v>62622</v>
+        <v>59472</v>
       </c>
       <c r="C47">
-        <v>31.311</v>
+        <v>29.736</v>
       </c>
       <c r="D47" t="str">
         <v>Normal</v>
@@ -5154,13 +5142,13 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B48">
-        <v>64123</v>
+        <v>61053</v>
       </c>
       <c r="C48">
-        <v>32.062</v>
+        <v>30.527</v>
       </c>
       <c r="D48" t="str">
         <v>Normal</v>
@@ -5168,13 +5156,13 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B49">
-        <v>65212</v>
+        <v>62622</v>
       </c>
       <c r="C49">
-        <v>32.606</v>
+        <v>31.311</v>
       </c>
       <c r="D49" t="str">
         <v>Normal</v>
@@ -5182,13 +5170,13 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B50">
-        <v>67712</v>
+        <v>64123</v>
       </c>
       <c r="C50">
-        <v>33.856</v>
+        <v>32.062</v>
       </c>
       <c r="D50" t="str">
         <v>Normal</v>
@@ -5196,13 +5184,13 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B51">
-        <v>68822</v>
+        <v>65212</v>
       </c>
       <c r="C51">
-        <v>34.411</v>
+        <v>32.606</v>
       </c>
       <c r="D51" t="str">
         <v>Normal</v>
@@ -5210,13 +5198,13 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B52">
-        <v>70442</v>
+        <v>67712</v>
       </c>
       <c r="C52">
-        <v>35.221</v>
+        <v>33.856</v>
       </c>
       <c r="D52" t="str">
         <v>Normal</v>
@@ -5224,13 +5212,13 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B53">
-        <v>72122</v>
+        <v>68822</v>
       </c>
       <c r="C53">
-        <v>36.061</v>
+        <v>34.411</v>
       </c>
       <c r="D53" t="str">
         <v>Normal</v>
@@ -5238,13 +5226,13 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B54">
-        <v>73832</v>
+        <v>70442</v>
       </c>
       <c r="C54">
-        <v>36.916</v>
+        <v>35.221</v>
       </c>
       <c r="D54" t="str">
         <v>Normal</v>
@@ -5252,13 +5240,13 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B55">
-        <v>75442</v>
+        <v>72122</v>
       </c>
       <c r="C55">
-        <v>37.721</v>
+        <v>36.061</v>
       </c>
       <c r="D55" t="str">
         <v>Normal</v>
@@ -5266,13 +5254,13 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B56">
-        <v>77063</v>
+        <v>73832</v>
       </c>
       <c r="C56">
-        <v>38.532</v>
+        <v>36.916</v>
       </c>
       <c r="D56" t="str">
         <v>Normal</v>
@@ -5280,13 +5268,13 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B57">
-        <v>78632</v>
+        <v>75442</v>
       </c>
       <c r="C57">
-        <v>39.316</v>
+        <v>37.721</v>
       </c>
       <c r="D57" t="str">
         <v>Normal</v>
@@ -5294,13 +5282,13 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B58">
-        <v>80142</v>
+        <v>77063</v>
       </c>
       <c r="C58">
-        <v>40.071</v>
+        <v>38.532</v>
       </c>
       <c r="D58" t="str">
         <v>Normal</v>
@@ -5308,13 +5296,13 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B59">
-        <v>81712</v>
+        <v>78632</v>
       </c>
       <c r="C59">
-        <v>40.856</v>
+        <v>39.316</v>
       </c>
       <c r="D59" t="str">
         <v>Normal</v>
@@ -5322,13 +5310,13 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B60">
-        <v>83272</v>
+        <v>80142</v>
       </c>
       <c r="C60">
-        <v>41.636</v>
+        <v>40.071</v>
       </c>
       <c r="D60" t="str">
         <v>Normal</v>
@@ -5336,13 +5324,13 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B61">
-        <v>84823</v>
+        <v>81712</v>
       </c>
       <c r="C61">
-        <v>42.412</v>
+        <v>40.856</v>
       </c>
       <c r="D61" t="str">
         <v>Normal</v>
@@ -5350,13 +5338,13 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B62">
-        <v>86447</v>
+        <v>83272</v>
       </c>
       <c r="C62">
-        <v>43.224</v>
+        <v>41.636</v>
       </c>
       <c r="D62" t="str">
         <v>Normal</v>
@@ -5364,13 +5352,13 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B63">
-        <v>88136</v>
+        <v>84823</v>
       </c>
       <c r="C63">
-        <v>44.068</v>
+        <v>42.412</v>
       </c>
       <c r="D63" t="str">
         <v>Normal</v>
@@ -5378,13 +5366,13 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B64">
-        <v>89807</v>
+        <v>86447</v>
       </c>
       <c r="C64">
-        <v>44.904</v>
+        <v>43.224</v>
       </c>
       <c r="D64" t="str">
         <v>Normal</v>
@@ -5392,13 +5380,13 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B65">
-        <v>91487</v>
+        <v>88136</v>
       </c>
       <c r="C65">
-        <v>45.744</v>
+        <v>44.068</v>
       </c>
       <c r="D65" t="str">
         <v>Normal</v>
@@ -5406,13 +5394,13 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B66">
-        <v>93117</v>
+        <v>89807</v>
       </c>
       <c r="C66">
-        <v>46.559</v>
+        <v>44.904</v>
       </c>
       <c r="D66" t="str">
         <v>Normal</v>
@@ -5420,13 +5408,13 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B67">
-        <v>94716</v>
+        <v>91487</v>
       </c>
       <c r="C67">
-        <v>47.358</v>
+        <v>45.744</v>
       </c>
       <c r="D67" t="str">
         <v>Normal</v>
@@ -5434,13 +5422,13 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B68">
-        <v>96287</v>
+        <v>93117</v>
       </c>
       <c r="C68">
-        <v>48.144</v>
+        <v>46.559</v>
       </c>
       <c r="D68" t="str">
         <v>Normal</v>
@@ -5448,13 +5436,13 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B69">
-        <v>97787</v>
+        <v>94716</v>
       </c>
       <c r="C69">
-        <v>48.894</v>
+        <v>47.358</v>
       </c>
       <c r="D69" t="str">
         <v>Normal</v>
@@ -5462,13 +5450,13 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B70">
-        <v>99327</v>
+        <v>96287</v>
       </c>
       <c r="C70">
-        <v>49.664</v>
+        <v>48.144</v>
       </c>
       <c r="D70" t="str">
         <v>Normal</v>
@@ -5476,13 +5464,13 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B71">
-        <v>100877</v>
+        <v>97787</v>
       </c>
       <c r="C71">
-        <v>50.439</v>
+        <v>48.894</v>
       </c>
       <c r="D71" t="str">
         <v>Normal</v>
@@ -5490,13 +5478,13 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B72">
-        <v>102487</v>
+        <v>99327</v>
       </c>
       <c r="C72">
-        <v>51.244</v>
+        <v>49.664</v>
       </c>
       <c r="D72" t="str">
         <v>Normal</v>
@@ -5504,13 +5492,13 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B73">
-        <v>104107</v>
+        <v>100877</v>
       </c>
       <c r="C73">
-        <v>52.054</v>
+        <v>50.439</v>
       </c>
       <c r="D73" t="str">
         <v>Normal</v>
@@ -5518,13 +5506,13 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B74">
-        <v>105776</v>
+        <v>102487</v>
       </c>
       <c r="C74">
-        <v>52.888</v>
+        <v>51.244</v>
       </c>
       <c r="D74" t="str">
         <v>Normal</v>
@@ -5532,13 +5520,13 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B75">
-        <v>107446</v>
+        <v>104107</v>
       </c>
       <c r="C75">
-        <v>53.723</v>
+        <v>52.054</v>
       </c>
       <c r="D75" t="str">
         <v>Normal</v>
@@ -5546,13 +5534,13 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B76">
-        <v>109116</v>
+        <v>105776</v>
       </c>
       <c r="C76">
-        <v>54.558</v>
+        <v>52.888</v>
       </c>
       <c r="D76" t="str">
         <v>Normal</v>
@@ -5560,13 +5548,13 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B77">
-        <v>110746</v>
+        <v>107446</v>
       </c>
       <c r="C77">
-        <v>55.373</v>
+        <v>53.723</v>
       </c>
       <c r="D77" t="str">
         <v>Normal</v>
@@ -5574,13 +5562,13 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B78">
-        <v>112267</v>
+        <v>109116</v>
       </c>
       <c r="C78">
-        <v>56.134</v>
+        <v>54.558</v>
       </c>
       <c r="D78" t="str">
         <v>Normal</v>
@@ -5588,13 +5576,13 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B79">
-        <v>113777</v>
+        <v>110746</v>
       </c>
       <c r="C79">
-        <v>56.889</v>
+        <v>55.373</v>
       </c>
       <c r="D79" t="str">
         <v>Normal</v>
@@ -5602,13 +5590,13 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B80">
-        <v>115316</v>
+        <v>112267</v>
       </c>
       <c r="C80">
-        <v>57.658</v>
+        <v>56.134</v>
       </c>
       <c r="D80" t="str">
         <v>Normal</v>
@@ -5616,13 +5604,13 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B81">
-        <v>116807</v>
+        <v>113777</v>
       </c>
       <c r="C81">
-        <v>58.404</v>
+        <v>56.889</v>
       </c>
       <c r="D81" t="str">
         <v>Normal</v>
@@ -5630,13 +5618,13 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B82">
-        <v>118386</v>
+        <v>115316</v>
       </c>
       <c r="C82">
-        <v>59.193</v>
+        <v>57.658</v>
       </c>
       <c r="D82" t="str">
         <v>Normal</v>
@@ -5644,13 +5632,13 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B83">
-        <v>120016</v>
+        <v>116807</v>
       </c>
       <c r="C83">
-        <v>60.008</v>
+        <v>58.404</v>
       </c>
       <c r="D83" t="str">
         <v>Normal</v>
@@ -5658,13 +5646,13 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B84">
-        <v>121716</v>
+        <v>118386</v>
       </c>
       <c r="C84">
-        <v>60.858</v>
+        <v>59.193</v>
       </c>
       <c r="D84" t="str">
         <v>Normal</v>
@@ -5672,13 +5660,13 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B85">
-        <v>123407</v>
+        <v>120016</v>
       </c>
       <c r="C85">
-        <v>61.704</v>
+        <v>60.008</v>
       </c>
       <c r="D85" t="str">
         <v>Normal</v>
@@ -5686,13 +5674,13 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B86">
-        <v>125067</v>
+        <v>121716</v>
       </c>
       <c r="C86">
-        <v>62.534</v>
+        <v>60.858</v>
       </c>
       <c r="D86" t="str">
         <v>Normal</v>
@@ -5700,13 +5688,13 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B87">
-        <v>126686</v>
+        <v>123407</v>
       </c>
       <c r="C87">
-        <v>63.343</v>
+        <v>61.704</v>
       </c>
       <c r="D87" t="str">
         <v>Normal</v>
@@ -5714,13 +5702,13 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B88">
-        <v>128256</v>
+        <v>125067</v>
       </c>
       <c r="C88">
-        <v>64.128</v>
+        <v>62.534</v>
       </c>
       <c r="D88" t="str">
         <v>Normal</v>
@@ -5728,13 +5716,13 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B89">
-        <v>129824</v>
+        <v>126686</v>
       </c>
       <c r="C89">
-        <v>64.912</v>
+        <v>63.343</v>
       </c>
       <c r="D89" t="str">
         <v>Normal</v>
@@ -5742,13 +5730,13 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B90">
-        <v>131334</v>
+        <v>128256</v>
       </c>
       <c r="C90">
-        <v>65.667</v>
+        <v>64.128</v>
       </c>
       <c r="D90" t="str">
         <v>Normal</v>
@@ -5756,13 +5744,13 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B91">
-        <v>132863</v>
+        <v>129824</v>
       </c>
       <c r="C91">
-        <v>66.432</v>
+        <v>64.912</v>
       </c>
       <c r="D91" t="str">
         <v>Normal</v>
@@ -5770,13 +5758,13 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B92">
-        <v>134433</v>
+        <v>131334</v>
       </c>
       <c r="C92">
-        <v>67.217</v>
+        <v>65.667</v>
       </c>
       <c r="D92" t="str">
         <v>Normal</v>
@@ -5784,13 +5772,13 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B93">
-        <v>136043</v>
+        <v>132863</v>
       </c>
       <c r="C93">
-        <v>68.022</v>
+        <v>66.432</v>
       </c>
       <c r="D93" t="str">
         <v>Normal</v>
@@ -5798,13 +5786,13 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B94">
-        <v>137684</v>
+        <v>134433</v>
       </c>
       <c r="C94">
-        <v>68.842</v>
+        <v>67.217</v>
       </c>
       <c r="D94" t="str">
         <v>Normal</v>
@@ -5812,13 +5800,13 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B95">
-        <v>139343</v>
+        <v>136043</v>
       </c>
       <c r="C95">
-        <v>69.672</v>
+        <v>68.022</v>
       </c>
       <c r="D95" t="str">
         <v>Normal</v>
@@ -5826,13 +5814,13 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B96">
-        <v>141013</v>
+        <v>137684</v>
       </c>
       <c r="C96">
-        <v>70.507</v>
+        <v>68.842</v>
       </c>
       <c r="D96" t="str">
         <v>Normal</v>
@@ -5840,13 +5828,13 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B97">
-        <v>142644</v>
+        <v>139343</v>
       </c>
       <c r="C97">
-        <v>71.322</v>
+        <v>69.672</v>
       </c>
       <c r="D97" t="str">
         <v>Normal</v>
@@ -5854,13 +5842,13 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B98">
-        <v>144274</v>
+        <v>141013</v>
       </c>
       <c r="C98">
-        <v>72.137</v>
+        <v>70.507</v>
       </c>
       <c r="D98" t="str">
         <v>Normal</v>
@@ -5868,13 +5856,13 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B99">
-        <v>145844</v>
+        <v>142644</v>
       </c>
       <c r="C99">
-        <v>72.922</v>
+        <v>71.322</v>
       </c>
       <c r="D99" t="str">
         <v>Normal</v>
@@ -5882,13 +5870,13 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B100">
-        <v>147373</v>
+        <v>144274</v>
       </c>
       <c r="C100">
-        <v>73.687</v>
+        <v>72.137</v>
       </c>
       <c r="D100" t="str">
         <v>Normal</v>
@@ -5896,13 +5884,13 @@
     </row>
     <row r="101">
       <c r="A101">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B101">
-        <v>148913</v>
+        <v>145844</v>
       </c>
       <c r="C101">
-        <v>74.457</v>
+        <v>72.922</v>
       </c>
       <c r="D101" t="str">
         <v>Normal</v>
@@ -5910,13 +5898,13 @@
     </row>
     <row r="102">
       <c r="A102">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B102">
-        <v>150453</v>
+        <v>147373</v>
       </c>
       <c r="C102">
-        <v>75.227</v>
+        <v>73.687</v>
       </c>
       <c r="D102" t="str">
         <v>Normal</v>
@@ -5924,13 +5912,13 @@
     </row>
     <row r="103">
       <c r="A103">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B103">
-        <v>152063</v>
+        <v>148913</v>
       </c>
       <c r="C103">
-        <v>76.032</v>
+        <v>74.457</v>
       </c>
       <c r="D103" t="str">
         <v>Normal</v>
@@ -5938,13 +5926,13 @@
     </row>
     <row r="104">
       <c r="A104">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B104">
-        <v>153694</v>
+        <v>150453</v>
       </c>
       <c r="C104">
-        <v>76.847</v>
+        <v>75.227</v>
       </c>
       <c r="D104" t="str">
         <v>Normal</v>
@@ -5952,13 +5940,13 @@
     </row>
     <row r="105">
       <c r="A105">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B105">
-        <v>155383</v>
+        <v>152063</v>
       </c>
       <c r="C105">
-        <v>77.692</v>
+        <v>76.032</v>
       </c>
       <c r="D105" t="str">
         <v>Normal</v>
@@ -5966,13 +5954,13 @@
     </row>
     <row r="106">
       <c r="A106">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B106">
-        <v>157033</v>
+        <v>153694</v>
       </c>
       <c r="C106">
-        <v>78.517</v>
+        <v>76.847</v>
       </c>
       <c r="D106" t="str">
         <v>Normal</v>
@@ -5980,13 +5968,13 @@
     </row>
     <row r="107">
       <c r="A107">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B107">
-        <v>158703</v>
+        <v>155383</v>
       </c>
       <c r="C107">
-        <v>79.352</v>
+        <v>77.692</v>
       </c>
       <c r="D107" t="str">
         <v>Normal</v>
@@ -5994,13 +5982,13 @@
     </row>
     <row r="108">
       <c r="A108">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B108">
-        <v>160283</v>
+        <v>157033</v>
       </c>
       <c r="C108">
-        <v>80.142</v>
+        <v>78.517</v>
       </c>
       <c r="D108" t="str">
         <v>Normal</v>
@@ -6008,13 +5996,13 @@
     </row>
     <row r="109">
       <c r="A109">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B109">
-        <v>161813</v>
+        <v>158703</v>
       </c>
       <c r="C109">
-        <v>80.907</v>
+        <v>79.352</v>
       </c>
       <c r="D109" t="str">
         <v>Normal</v>
@@ -6022,13 +6010,13 @@
     </row>
     <row r="110">
       <c r="A110">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B110">
-        <v>163334</v>
+        <v>160283</v>
       </c>
       <c r="C110">
-        <v>81.667</v>
+        <v>80.142</v>
       </c>
       <c r="D110" t="str">
         <v>Normal</v>
@@ -6036,13 +6024,13 @@
     </row>
     <row r="111">
       <c r="A111">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B111">
-        <v>164834</v>
+        <v>161813</v>
       </c>
       <c r="C111">
-        <v>82.417</v>
+        <v>80.907</v>
       </c>
       <c r="D111" t="str">
         <v>Normal</v>
@@ -6050,13 +6038,13 @@
     </row>
     <row r="112">
       <c r="A112">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B112">
-        <v>166373</v>
+        <v>163334</v>
       </c>
       <c r="C112">
-        <v>83.187</v>
+        <v>81.667</v>
       </c>
       <c r="D112" t="str">
         <v>Normal</v>
@@ -6064,13 +6052,13 @@
     </row>
     <row r="113">
       <c r="A113">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B113">
-        <v>167993</v>
+        <v>164834</v>
       </c>
       <c r="C113">
-        <v>83.997</v>
+        <v>82.417</v>
       </c>
       <c r="D113" t="str">
         <v>Normal</v>
@@ -6078,13 +6066,13 @@
     </row>
     <row r="114">
       <c r="A114">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B114">
-        <v>169584</v>
+        <v>166373</v>
       </c>
       <c r="C114">
-        <v>84.792</v>
+        <v>83.187</v>
       </c>
       <c r="D114" t="str">
         <v>Normal</v>
@@ -6092,13 +6080,13 @@
     </row>
     <row r="115">
       <c r="A115">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B115">
-        <v>171224</v>
+        <v>167993</v>
       </c>
       <c r="C115">
-        <v>85.612</v>
+        <v>83.997</v>
       </c>
       <c r="D115" t="str">
         <v>Normal</v>
@@ -6106,13 +6094,13 @@
     </row>
     <row r="116">
       <c r="A116">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B116">
-        <v>172912</v>
+        <v>169584</v>
       </c>
       <c r="C116">
-        <v>86.456</v>
+        <v>84.792</v>
       </c>
       <c r="D116" t="str">
         <v>Normal</v>
@@ -6120,13 +6108,13 @@
     </row>
     <row r="117">
       <c r="A117">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B117">
-        <v>174592</v>
+        <v>171224</v>
       </c>
       <c r="C117">
-        <v>87.296</v>
+        <v>85.612</v>
       </c>
       <c r="D117" t="str">
         <v>Normal</v>
@@ -6134,13 +6122,13 @@
     </row>
     <row r="118">
       <c r="A118">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B118">
-        <v>176232</v>
+        <v>172912</v>
       </c>
       <c r="C118">
-        <v>88.116</v>
+        <v>86.456</v>
       </c>
       <c r="D118" t="str">
         <v>Normal</v>
@@ -6148,13 +6136,13 @@
     </row>
     <row r="119">
       <c r="A119">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B119">
-        <v>177823</v>
+        <v>174592</v>
       </c>
       <c r="C119">
-        <v>88.912</v>
+        <v>87.296</v>
       </c>
       <c r="D119" t="str">
         <v>Normal</v>
@@ -6162,13 +6150,13 @@
     </row>
     <row r="120">
       <c r="A120">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B120">
-        <v>179393</v>
+        <v>176232</v>
       </c>
       <c r="C120">
-        <v>89.697</v>
+        <v>88.116</v>
       </c>
       <c r="D120" t="str">
         <v>Normal</v>
@@ -6176,13 +6164,13 @@
     </row>
     <row r="121">
       <c r="A121">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B121">
-        <v>180932</v>
+        <v>177823</v>
       </c>
       <c r="C121">
-        <v>90.466</v>
+        <v>88.912</v>
       </c>
       <c r="D121" t="str">
         <v>Normal</v>
@@ -6190,13 +6178,13 @@
     </row>
     <row r="122">
       <c r="A122">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B122">
-        <v>182432</v>
+        <v>179393</v>
       </c>
       <c r="C122">
-        <v>91.216</v>
+        <v>89.697</v>
       </c>
       <c r="D122" t="str">
         <v>Normal</v>
@@ -6204,13 +6192,13 @@
     </row>
     <row r="123">
       <c r="A123">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B123">
-        <v>183973</v>
+        <v>180932</v>
       </c>
       <c r="C123">
-        <v>91.987</v>
+        <v>90.466</v>
       </c>
       <c r="D123" t="str">
         <v>Normal</v>
@@ -6218,13 +6206,13 @@
     </row>
     <row r="124">
       <c r="A124">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B124">
-        <v>185572</v>
+        <v>182432</v>
       </c>
       <c r="C124">
-        <v>92.786</v>
+        <v>91.216</v>
       </c>
       <c r="D124" t="str">
         <v>Normal</v>
@@ -6232,13 +6220,13 @@
     </row>
     <row r="125">
       <c r="A125">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B125">
-        <v>187182</v>
+        <v>183973</v>
       </c>
       <c r="C125">
-        <v>93.591</v>
+        <v>91.987</v>
       </c>
       <c r="D125" t="str">
         <v>Normal</v>
@@ -6246,13 +6234,13 @@
     </row>
     <row r="126">
       <c r="A126">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B126">
-        <v>188853</v>
+        <v>185572</v>
       </c>
       <c r="C126">
-        <v>94.427</v>
+        <v>92.786</v>
       </c>
       <c r="D126" t="str">
         <v>Normal</v>
@@ -6260,13 +6248,13 @@
     </row>
     <row r="127">
       <c r="A127">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B127">
-        <v>190513</v>
+        <v>187182</v>
       </c>
       <c r="C127">
-        <v>95.257</v>
+        <v>93.591</v>
       </c>
       <c r="D127" t="str">
         <v>Normal</v>
@@ -6274,13 +6262,13 @@
     </row>
     <row r="128">
       <c r="A128">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B128">
-        <v>192202</v>
+        <v>188853</v>
       </c>
       <c r="C128">
-        <v>96.101</v>
+        <v>94.427</v>
       </c>
       <c r="D128" t="str">
         <v>Normal</v>
@@ -6288,13 +6276,13 @@
     </row>
     <row r="129">
       <c r="A129">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B129">
-        <v>193822</v>
+        <v>190513</v>
       </c>
       <c r="C129">
-        <v>96.911</v>
+        <v>95.257</v>
       </c>
       <c r="D129" t="str">
         <v>Normal</v>
@@ -6302,13 +6290,13 @@
     </row>
     <row r="130">
       <c r="A130">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B130">
-        <v>195402</v>
+        <v>192202</v>
       </c>
       <c r="C130">
-        <v>97.701</v>
+        <v>96.101</v>
       </c>
       <c r="D130" t="str">
         <v>Normal</v>
@@ -6316,13 +6304,13 @@
     </row>
     <row r="131">
       <c r="A131">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B131">
-        <v>196922</v>
+        <v>193822</v>
       </c>
       <c r="C131">
-        <v>98.461</v>
+        <v>96.911</v>
       </c>
       <c r="D131" t="str">
         <v>Normal</v>
@@ -6330,13 +6318,13 @@
     </row>
     <row r="132">
       <c r="A132">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B132">
-        <v>198442</v>
+        <v>195402</v>
       </c>
       <c r="C132">
-        <v>99.221</v>
+        <v>97.701</v>
       </c>
       <c r="D132" t="str">
         <v>Normal</v>
@@ -6344,13 +6332,13 @@
     </row>
     <row r="133">
       <c r="A133">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B133">
-        <v>199922</v>
+        <v>196922</v>
       </c>
       <c r="C133">
-        <v>99.961</v>
+        <v>98.461</v>
       </c>
       <c r="D133" t="str">
         <v>Normal</v>
@@ -6358,13 +6346,13 @@
     </row>
     <row r="134">
       <c r="A134">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B134">
-        <v>201463</v>
+        <v>198442</v>
       </c>
       <c r="C134">
-        <v>100.732</v>
+        <v>99.221</v>
       </c>
       <c r="D134" t="str">
         <v>Normal</v>
@@ -6372,13 +6360,13 @@
     </row>
     <row r="135">
       <c r="A135">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B135">
-        <v>203092</v>
+        <v>199922</v>
       </c>
       <c r="C135">
-        <v>101.546</v>
+        <v>99.961</v>
       </c>
       <c r="D135" t="str">
         <v>Normal</v>
@@ -6386,13 +6374,13 @@
     </row>
     <row r="136">
       <c r="A136">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B136">
-        <v>204693</v>
+        <v>201463</v>
       </c>
       <c r="C136">
-        <v>102.347</v>
+        <v>100.732</v>
       </c>
       <c r="D136" t="str">
         <v>Normal</v>
@@ -6400,13 +6388,13 @@
     </row>
     <row r="137">
       <c r="A137">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B137">
-        <v>206393</v>
+        <v>203092</v>
       </c>
       <c r="C137">
-        <v>103.197</v>
+        <v>101.546</v>
       </c>
       <c r="D137" t="str">
         <v>Normal</v>
@@ -6414,13 +6402,13 @@
     </row>
     <row r="138">
       <c r="A138">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B138">
-        <v>208023</v>
+        <v>204693</v>
       </c>
       <c r="C138">
-        <v>104.012</v>
+        <v>102.347</v>
       </c>
       <c r="D138" t="str">
         <v>Normal</v>
@@ -6428,13 +6416,13 @@
     </row>
     <row r="139">
       <c r="A139">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B139">
-        <v>209683</v>
+        <v>206393</v>
       </c>
       <c r="C139">
-        <v>104.842</v>
+        <v>103.197</v>
       </c>
       <c r="D139" t="str">
         <v>Normal</v>
@@ -6442,13 +6430,13 @@
     </row>
     <row r="140">
       <c r="A140">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B140">
-        <v>211262</v>
+        <v>208023</v>
       </c>
       <c r="C140">
-        <v>105.631</v>
+        <v>104.012</v>
       </c>
       <c r="D140" t="str">
         <v>Normal</v>
@@ -6456,13 +6444,13 @@
     </row>
     <row r="141">
       <c r="A141">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B141">
-        <v>212832</v>
+        <v>209683</v>
       </c>
       <c r="C141">
-        <v>106.416</v>
+        <v>104.842</v>
       </c>
       <c r="D141" t="str">
         <v>Normal</v>
@@ -6470,13 +6458,13 @@
     </row>
     <row r="142">
       <c r="A142">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B142">
-        <v>214353</v>
+        <v>211262</v>
       </c>
       <c r="C142">
-        <v>107.177</v>
+        <v>105.631</v>
       </c>
       <c r="D142" t="str">
         <v>Normal</v>
@@ -6484,13 +6472,13 @@
     </row>
     <row r="143">
       <c r="A143">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B143">
-        <v>215833</v>
+        <v>212832</v>
       </c>
       <c r="C143">
-        <v>107.917</v>
+        <v>106.416</v>
       </c>
       <c r="D143" t="str">
         <v>Normal</v>
@@ -6498,13 +6486,13 @@
     </row>
     <row r="144">
       <c r="A144">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B144">
-        <v>217413</v>
+        <v>214353</v>
       </c>
       <c r="C144">
-        <v>108.707</v>
+        <v>107.177</v>
       </c>
       <c r="D144" t="str">
         <v>Normal</v>
@@ -6512,13 +6500,13 @@
     </row>
     <row r="145">
       <c r="A145">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B145">
-        <v>219043</v>
+        <v>215833</v>
       </c>
       <c r="C145">
-        <v>109.522</v>
+        <v>107.917</v>
       </c>
       <c r="D145" t="str">
         <v>Normal</v>
@@ -6526,13 +6514,13 @@
     </row>
     <row r="146">
       <c r="A146">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B146">
-        <v>220683</v>
+        <v>217413</v>
       </c>
       <c r="C146">
-        <v>110.342</v>
+        <v>108.707</v>
       </c>
       <c r="D146" t="str">
         <v>Normal</v>
@@ -6540,13 +6528,13 @@
     </row>
     <row r="147">
       <c r="A147">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B147">
-        <v>222344</v>
+        <v>219043</v>
       </c>
       <c r="C147">
-        <v>111.172</v>
+        <v>109.522</v>
       </c>
       <c r="D147" t="str">
         <v>Normal</v>
@@ -6554,13 +6542,13 @@
     </row>
     <row r="148">
       <c r="A148">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B148">
-        <v>224023</v>
+        <v>220683</v>
       </c>
       <c r="C148">
-        <v>112.012</v>
+        <v>110.342</v>
       </c>
       <c r="D148" t="str">
         <v>Normal</v>
@@ -6568,13 +6556,13 @@
     </row>
     <row r="149">
       <c r="A149">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B149">
-        <v>225654</v>
+        <v>222344</v>
       </c>
       <c r="C149">
-        <v>112.827</v>
+        <v>111.172</v>
       </c>
       <c r="D149" t="str">
         <v>Normal</v>
@@ -6582,13 +6570,13 @@
     </row>
     <row r="150">
       <c r="A150">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B150">
-        <v>227303</v>
+        <v>224023</v>
       </c>
       <c r="C150">
-        <v>113.652</v>
+        <v>112.012</v>
       </c>
       <c r="D150" t="str">
         <v>Normal</v>
@@ -6596,13 +6584,13 @@
     </row>
     <row r="151">
       <c r="A151">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B151">
-        <v>228854</v>
+        <v>225654</v>
       </c>
       <c r="C151">
-        <v>114.427</v>
+        <v>112.827</v>
       </c>
       <c r="D151" t="str">
         <v>Normal</v>
@@ -6610,13 +6598,13 @@
     </row>
     <row r="152">
       <c r="A152">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B152">
-        <v>230393</v>
+        <v>227303</v>
       </c>
       <c r="C152">
-        <v>115.197</v>
+        <v>113.652</v>
       </c>
       <c r="D152" t="str">
         <v>Normal</v>
@@ -6624,13 +6612,13 @@
     </row>
     <row r="153">
       <c r="A153">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B153">
-        <v>231893</v>
+        <v>228854</v>
       </c>
       <c r="C153">
-        <v>115.947</v>
+        <v>114.427</v>
       </c>
       <c r="D153" t="str">
         <v>Normal</v>
@@ -6638,13 +6626,13 @@
     </row>
     <row r="154">
       <c r="A154">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B154">
-        <v>233413</v>
+        <v>230393</v>
       </c>
       <c r="C154">
-        <v>116.707</v>
+        <v>115.197</v>
       </c>
       <c r="D154" t="str">
         <v>Normal</v>
@@ -6652,13 +6640,13 @@
     </row>
     <row r="155">
       <c r="A155">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B155">
-        <v>234953</v>
+        <v>231893</v>
       </c>
       <c r="C155">
-        <v>117.477</v>
+        <v>115.947</v>
       </c>
       <c r="D155" t="str">
         <v>Normal</v>
@@ -6666,13 +6654,13 @@
     </row>
     <row r="156">
       <c r="A156">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B156">
-        <v>236603</v>
+        <v>233413</v>
       </c>
       <c r="C156">
-        <v>118.302</v>
+        <v>116.707</v>
       </c>
       <c r="D156" t="str">
         <v>Normal</v>
@@ -6680,13 +6668,13 @@
     </row>
     <row r="157">
       <c r="A157">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B157">
-        <v>238254</v>
+        <v>234953</v>
       </c>
       <c r="C157">
-        <v>119.127</v>
+        <v>117.477</v>
       </c>
       <c r="D157" t="str">
         <v>Normal</v>
@@ -6694,13 +6682,13 @@
     </row>
     <row r="158">
       <c r="A158">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B158">
-        <v>239963</v>
+        <v>236603</v>
       </c>
       <c r="C158">
-        <v>119.982</v>
+        <v>118.302</v>
       </c>
       <c r="D158" t="str">
         <v>Normal</v>
@@ -6708,13 +6696,13 @@
     </row>
     <row r="159">
       <c r="A159">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B159">
-        <v>241633</v>
+        <v>238254</v>
       </c>
       <c r="C159">
-        <v>120.817</v>
+        <v>119.127</v>
       </c>
       <c r="D159" t="str">
         <v>Normal</v>
@@ -6722,13 +6710,13 @@
     </row>
     <row r="160">
       <c r="A160">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B160">
-        <v>243253</v>
+        <v>239963</v>
       </c>
       <c r="C160">
-        <v>121.627</v>
+        <v>119.982</v>
       </c>
       <c r="D160" t="str">
         <v>Normal</v>
@@ -6736,13 +6724,13 @@
     </row>
     <row r="161">
       <c r="A161">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B161">
-        <v>244834</v>
+        <v>241633</v>
       </c>
       <c r="C161">
-        <v>122.417</v>
+        <v>120.817</v>
       </c>
       <c r="D161" t="str">
         <v>Normal</v>
@@ -6750,13 +6738,13 @@
     </row>
     <row r="162">
       <c r="A162">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B162">
-        <v>246373</v>
+        <v>243253</v>
       </c>
       <c r="C162">
-        <v>123.187</v>
+        <v>121.627</v>
       </c>
       <c r="D162" t="str">
         <v>Normal</v>
@@ -6764,13 +6752,13 @@
     </row>
     <row r="163">
       <c r="A163">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B163">
-        <v>247894</v>
+        <v>244834</v>
       </c>
       <c r="C163">
-        <v>123.947</v>
+        <v>122.417</v>
       </c>
       <c r="D163" t="str">
         <v>Normal</v>
@@ -6778,13 +6766,13 @@
     </row>
     <row r="164">
       <c r="A164">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B164">
-        <v>249413</v>
+        <v>246373</v>
       </c>
       <c r="C164">
-        <v>124.707</v>
+        <v>123.187</v>
       </c>
       <c r="D164" t="str">
         <v>Normal</v>
@@ -6792,13 +6780,13 @@
     </row>
     <row r="165">
       <c r="A165">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B165">
-        <v>250953</v>
+        <v>247894</v>
       </c>
       <c r="C165">
-        <v>125.477</v>
+        <v>123.947</v>
       </c>
       <c r="D165" t="str">
         <v>Normal</v>
@@ -6806,13 +6794,13 @@
     </row>
     <row r="166">
       <c r="A166">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B166">
-        <v>252514</v>
+        <v>249413</v>
       </c>
       <c r="C166">
-        <v>126.257</v>
+        <v>124.707</v>
       </c>
       <c r="D166" t="str">
         <v>Normal</v>
@@ -6820,13 +6808,13 @@
     </row>
     <row r="167">
       <c r="A167">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B167">
-        <v>254143</v>
+        <v>250953</v>
       </c>
       <c r="C167">
-        <v>127.072</v>
+        <v>125.477</v>
       </c>
       <c r="D167" t="str">
         <v>Normal</v>
@@ -6834,13 +6822,13 @@
     </row>
     <row r="168">
       <c r="A168">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B168">
-        <v>255853</v>
+        <v>252514</v>
       </c>
       <c r="C168">
-        <v>127.927</v>
+        <v>126.257</v>
       </c>
       <c r="D168" t="str">
         <v>Normal</v>
@@ -6848,13 +6836,13 @@
     </row>
     <row r="169">
       <c r="A169">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B169">
-        <v>257507</v>
+        <v>254143</v>
       </c>
       <c r="C169">
-        <v>128.754</v>
+        <v>127.072</v>
       </c>
       <c r="D169" t="str">
         <v>Normal</v>
@@ -6862,13 +6850,13 @@
     </row>
     <row r="170">
       <c r="A170">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B170">
-        <v>259137</v>
+        <v>255853</v>
       </c>
       <c r="C170">
-        <v>129.569</v>
+        <v>127.927</v>
       </c>
       <c r="D170" t="str">
         <v>Normal</v>
@@ -6876,13 +6864,13 @@
     </row>
     <row r="171">
       <c r="A171">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B171">
-        <v>260766</v>
+        <v>257507</v>
       </c>
       <c r="C171">
-        <v>130.383</v>
+        <v>128.754</v>
       </c>
       <c r="D171" t="str">
         <v>Normal</v>
@@ -6890,13 +6878,13 @@
     </row>
     <row r="172">
       <c r="A172">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B172">
-        <v>262367</v>
+        <v>259137</v>
       </c>
       <c r="C172">
-        <v>131.184</v>
+        <v>129.569</v>
       </c>
       <c r="D172" t="str">
         <v>Normal</v>
@@ -6904,13 +6892,13 @@
     </row>
     <row r="173">
       <c r="A173">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B173">
-        <v>263866</v>
+        <v>260766</v>
       </c>
       <c r="C173">
-        <v>131.933</v>
+        <v>130.383</v>
       </c>
       <c r="D173" t="str">
         <v>Normal</v>
@@ -6918,13 +6906,13 @@
     </row>
     <row r="174">
       <c r="A174">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B174">
-        <v>265377</v>
+        <v>262367</v>
       </c>
       <c r="C174">
-        <v>132.689</v>
+        <v>131.184</v>
       </c>
       <c r="D174" t="str">
         <v>Normal</v>
@@ -6932,13 +6920,13 @@
     </row>
     <row r="175">
       <c r="A175">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B175">
-        <v>266897</v>
+        <v>263866</v>
       </c>
       <c r="C175">
-        <v>133.449</v>
+        <v>131.933</v>
       </c>
       <c r="D175" t="str">
         <v>Normal</v>
@@ -6946,13 +6934,13 @@
     </row>
     <row r="176">
       <c r="A176">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B176">
-        <v>268427</v>
+        <v>265377</v>
       </c>
       <c r="C176">
-        <v>134.214</v>
+        <v>132.689</v>
       </c>
       <c r="D176" t="str">
         <v>Normal</v>
@@ -6960,13 +6948,13 @@
     </row>
     <row r="177">
       <c r="A177">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B177">
-        <v>270067</v>
+        <v>266897</v>
       </c>
       <c r="C177">
-        <v>135.034</v>
+        <v>133.449</v>
       </c>
       <c r="D177" t="str">
         <v>Normal</v>
@@ -6974,13 +6962,13 @@
     </row>
     <row r="178">
       <c r="A178">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B178">
-        <v>271727</v>
+        <v>268427</v>
       </c>
       <c r="C178">
-        <v>135.864</v>
+        <v>134.214</v>
       </c>
       <c r="D178" t="str">
         <v>Normal</v>
@@ -6988,13 +6976,13 @@
     </row>
     <row r="179">
       <c r="A179">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B179">
-        <v>273407</v>
+        <v>270067</v>
       </c>
       <c r="C179">
-        <v>136.704</v>
+        <v>135.034</v>
       </c>
       <c r="D179" t="str">
         <v>Normal</v>
@@ -7002,13 +6990,13 @@
     </row>
     <row r="180">
       <c r="A180">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B180">
-        <v>275066</v>
+        <v>271727</v>
       </c>
       <c r="C180">
-        <v>137.533</v>
+        <v>135.864</v>
       </c>
       <c r="D180" t="str">
         <v>Normal</v>
@@ -7016,13 +7004,13 @@
     </row>
     <row r="181">
       <c r="A181">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B181">
-        <v>276707</v>
+        <v>273407</v>
       </c>
       <c r="C181">
-        <v>138.354</v>
+        <v>136.704</v>
       </c>
       <c r="D181" t="str">
         <v>Normal</v>
@@ -7030,13 +7018,13 @@
     </row>
     <row r="182">
       <c r="A182">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B182">
-        <v>278287</v>
+        <v>275066</v>
       </c>
       <c r="C182">
-        <v>139.144</v>
+        <v>137.533</v>
       </c>
       <c r="D182" t="str">
         <v>Normal</v>
@@ -7044,13 +7032,13 @@
     </row>
     <row r="183">
       <c r="A183">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B183">
-        <v>279836</v>
+        <v>276707</v>
       </c>
       <c r="C183">
-        <v>139.918</v>
+        <v>138.354</v>
       </c>
       <c r="D183" t="str">
         <v>Normal</v>
@@ -7058,13 +7046,13 @@
     </row>
     <row r="184">
       <c r="A184">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B184">
-        <v>281327</v>
+        <v>278287</v>
       </c>
       <c r="C184">
-        <v>140.664</v>
+        <v>139.144</v>
       </c>
       <c r="D184" t="str">
         <v>Normal</v>
@@ -7072,13 +7060,13 @@
     </row>
     <row r="185">
       <c r="A185">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B185">
-        <v>282826</v>
+        <v>279836</v>
       </c>
       <c r="C185">
-        <v>141.413</v>
+        <v>139.918</v>
       </c>
       <c r="D185" t="str">
         <v>Normal</v>
@@ -7086,13 +7074,13 @@
     </row>
     <row r="186">
       <c r="A186">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B186">
-        <v>284407</v>
+        <v>281327</v>
       </c>
       <c r="C186">
-        <v>142.204</v>
+        <v>140.664</v>
       </c>
       <c r="D186" t="str">
         <v>Normal</v>
@@ -7100,13 +7088,13 @@
     </row>
     <row r="187">
       <c r="A187">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B187">
-        <v>285997</v>
+        <v>282826</v>
       </c>
       <c r="C187">
-        <v>142.999</v>
+        <v>141.413</v>
       </c>
       <c r="D187" t="str">
         <v>Normal</v>
@@ -7114,13 +7102,13 @@
     </row>
     <row r="188">
       <c r="A188">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B188">
-        <v>287647</v>
+        <v>284407</v>
       </c>
       <c r="C188">
-        <v>143.824</v>
+        <v>142.204</v>
       </c>
       <c r="D188" t="str">
         <v>Normal</v>
@@ -7128,13 +7116,13 @@
     </row>
     <row r="189">
       <c r="A189">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B189">
-        <v>289317</v>
+        <v>285997</v>
       </c>
       <c r="C189">
-        <v>144.659</v>
+        <v>142.999</v>
       </c>
       <c r="D189" t="str">
         <v>Normal</v>
@@ -7142,13 +7130,13 @@
     </row>
     <row r="190">
       <c r="A190">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B190">
-        <v>290987</v>
+        <v>287647</v>
       </c>
       <c r="C190">
-        <v>145.494</v>
+        <v>143.824</v>
       </c>
       <c r="D190" t="str">
         <v>Normal</v>
@@ -7156,13 +7144,13 @@
     </row>
     <row r="191">
       <c r="A191">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B191">
-        <v>292627</v>
+        <v>289317</v>
       </c>
       <c r="C191">
-        <v>146.314</v>
+        <v>144.659</v>
       </c>
       <c r="D191" t="str">
         <v>Normal</v>
@@ -7170,13 +7158,13 @@
     </row>
     <row r="192">
       <c r="A192">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B192">
-        <v>294257</v>
+        <v>290987</v>
       </c>
       <c r="C192">
-        <v>147.129</v>
+        <v>145.494</v>
       </c>
       <c r="D192" t="str">
         <v>Normal</v>
@@ -7184,13 +7172,13 @@
     </row>
     <row r="193">
       <c r="A193">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B193">
-        <v>295817</v>
+        <v>292627</v>
       </c>
       <c r="C193">
-        <v>147.909</v>
+        <v>146.314</v>
       </c>
       <c r="D193" t="str">
         <v>Normal</v>
@@ -7198,13 +7186,13 @@
     </row>
     <row r="194">
       <c r="A194">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B194">
-        <v>297346</v>
+        <v>294257</v>
       </c>
       <c r="C194">
-        <v>148.673</v>
+        <v>147.129</v>
       </c>
       <c r="D194" t="str">
         <v>Normal</v>
@@ -7212,13 +7200,13 @@
     </row>
     <row r="195">
       <c r="A195">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B195">
-        <v>298866</v>
+        <v>295817</v>
       </c>
       <c r="C195">
-        <v>149.433</v>
+        <v>147.909</v>
       </c>
       <c r="D195" t="str">
         <v>Normal</v>
@@ -7226,13 +7214,13 @@
     </row>
     <row r="196">
       <c r="A196">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B196">
-        <v>300423</v>
+        <v>297346</v>
       </c>
       <c r="C196">
-        <v>150.212</v>
+        <v>148.673</v>
       </c>
       <c r="D196" t="str">
         <v>Normal</v>
@@ -7240,13 +7228,13 @@
     </row>
     <row r="197">
       <c r="A197">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B197">
-        <v>302022</v>
+        <v>298866</v>
       </c>
       <c r="C197">
-        <v>151.011</v>
+        <v>149.433</v>
       </c>
       <c r="D197" t="str">
         <v>Normal</v>
@@ -7254,13 +7242,13 @@
     </row>
     <row r="198">
       <c r="A198">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B198">
-        <v>303652</v>
+        <v>300423</v>
       </c>
       <c r="C198">
-        <v>151.826</v>
+        <v>150.212</v>
       </c>
       <c r="D198" t="str">
         <v>Normal</v>
@@ -7268,13 +7256,13 @@
     </row>
     <row r="199">
       <c r="A199">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B199">
-        <v>305302</v>
+        <v>302022</v>
       </c>
       <c r="C199">
-        <v>152.651</v>
+        <v>151.011</v>
       </c>
       <c r="D199" t="str">
         <v>Normal</v>
@@ -7282,13 +7270,13 @@
     </row>
     <row r="200">
       <c r="A200">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B200">
-        <v>306952</v>
+        <v>303652</v>
       </c>
       <c r="C200">
-        <v>153.476</v>
+        <v>151.826</v>
       </c>
       <c r="D200" t="str">
         <v>Normal</v>
@@ -7296,13 +7284,13 @@
     </row>
     <row r="201">
       <c r="A201">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B201">
-        <v>308642</v>
+        <v>305302</v>
       </c>
       <c r="C201">
-        <v>154.321</v>
+        <v>152.651</v>
       </c>
       <c r="D201" t="str">
         <v>Normal</v>
@@ -7310,13 +7298,13 @@
     </row>
     <row r="202">
       <c r="A202">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B202">
-        <v>310293</v>
+        <v>306952</v>
       </c>
       <c r="C202">
-        <v>155.147</v>
+        <v>153.476</v>
       </c>
       <c r="D202" t="str">
         <v>Normal</v>
@@ -7324,13 +7312,13 @@
     </row>
     <row r="203">
       <c r="A203">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B203">
-        <v>311882</v>
+        <v>308642</v>
       </c>
       <c r="C203">
-        <v>155.941</v>
+        <v>154.321</v>
       </c>
       <c r="D203" t="str">
         <v>Normal</v>
@@ -7338,13 +7326,13 @@
     </row>
     <row r="204">
       <c r="A204">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B204">
-        <v>313442</v>
+        <v>310293</v>
       </c>
       <c r="C204">
-        <v>156.721</v>
+        <v>155.147</v>
       </c>
       <c r="D204" t="str">
         <v>Normal</v>
@@ -7352,13 +7340,13 @@
     </row>
     <row r="205">
       <c r="A205">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B205">
-        <v>314982</v>
+        <v>311882</v>
       </c>
       <c r="C205">
-        <v>157.491</v>
+        <v>155.941</v>
       </c>
       <c r="D205" t="str">
         <v>Normal</v>
@@ -7366,13 +7354,13 @@
     </row>
     <row r="206">
       <c r="A206">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B206">
-        <v>316522</v>
+        <v>313442</v>
       </c>
       <c r="C206">
-        <v>158.261</v>
+        <v>156.721</v>
       </c>
       <c r="D206" t="str">
         <v>Normal</v>
@@ -7380,13 +7368,13 @@
     </row>
     <row r="207">
       <c r="A207">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B207">
-        <v>318102</v>
+        <v>314982</v>
       </c>
       <c r="C207">
-        <v>159.051</v>
+        <v>157.491</v>
       </c>
       <c r="D207" t="str">
         <v>Normal</v>
@@ -7394,13 +7382,13 @@
     </row>
     <row r="208">
       <c r="A208">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B208">
-        <v>319692</v>
+        <v>316522</v>
       </c>
       <c r="C208">
-        <v>159.846</v>
+        <v>158.261</v>
       </c>
       <c r="D208" t="str">
         <v>Normal</v>
@@ -7408,13 +7396,13 @@
     </row>
     <row r="209">
       <c r="A209">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B209">
-        <v>321373</v>
+        <v>318102</v>
       </c>
       <c r="C209">
-        <v>160.687</v>
+        <v>159.051</v>
       </c>
       <c r="D209" t="str">
         <v>Normal</v>
@@ -7422,13 +7410,13 @@
     </row>
     <row r="210">
       <c r="A210">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B210">
-        <v>323022</v>
+        <v>319692</v>
       </c>
       <c r="C210">
-        <v>161.511</v>
+        <v>159.846</v>
       </c>
       <c r="D210" t="str">
         <v>Normal</v>
@@ -7436,13 +7424,13 @@
     </row>
     <row r="211">
       <c r="A211">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B211">
-        <v>324722</v>
+        <v>321373</v>
       </c>
       <c r="C211">
-        <v>162.361</v>
+        <v>160.687</v>
       </c>
       <c r="D211" t="str">
         <v>Normal</v>
@@ -7450,13 +7438,13 @@
     </row>
     <row r="212">
       <c r="A212">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B212">
-        <v>326382</v>
+        <v>323022</v>
       </c>
       <c r="C212">
-        <v>163.191</v>
+        <v>161.511</v>
       </c>
       <c r="D212" t="str">
         <v>Normal</v>
@@ -7464,13 +7452,13 @@
     </row>
     <row r="213">
       <c r="A213">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B213">
-        <v>328012</v>
+        <v>324722</v>
       </c>
       <c r="C213">
-        <v>164.006</v>
+        <v>162.361</v>
       </c>
       <c r="D213" t="str">
         <v>Normal</v>
@@ -7478,13 +7466,13 @@
     </row>
     <row r="214">
       <c r="A214">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B214">
-        <v>329622</v>
+        <v>326382</v>
       </c>
       <c r="C214">
-        <v>164.811</v>
+        <v>163.191</v>
       </c>
       <c r="D214" t="str">
         <v>Normal</v>
@@ -7492,13 +7480,13 @@
     </row>
     <row r="215">
       <c r="A215">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B215">
-        <v>331192</v>
+        <v>328012</v>
       </c>
       <c r="C215">
-        <v>165.596</v>
+        <v>164.006</v>
       </c>
       <c r="D215" t="str">
         <v>Normal</v>
@@ -7506,13 +7494,13 @@
     </row>
     <row r="216">
       <c r="A216">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B216">
-        <v>332682</v>
+        <v>329622</v>
       </c>
       <c r="C216">
-        <v>166.341</v>
+        <v>164.811</v>
       </c>
       <c r="D216" t="str">
         <v>Normal</v>
@@ -7520,13 +7508,13 @@
     </row>
     <row r="217">
       <c r="A217">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B217">
-        <v>334182</v>
+        <v>331192</v>
       </c>
       <c r="C217">
-        <v>167.091</v>
+        <v>165.596</v>
       </c>
       <c r="D217" t="str">
         <v>Normal</v>
@@ -7534,13 +7522,13 @@
     </row>
     <row r="218">
       <c r="A218">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B218">
-        <v>335782</v>
+        <v>332682</v>
       </c>
       <c r="C218">
-        <v>167.891</v>
+        <v>166.341</v>
       </c>
       <c r="D218" t="str">
         <v>Normal</v>
@@ -7548,13 +7536,13 @@
     </row>
     <row r="219">
       <c r="A219">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B219">
-        <v>337382</v>
+        <v>334182</v>
       </c>
       <c r="C219">
-        <v>168.691</v>
+        <v>167.091</v>
       </c>
       <c r="D219" t="str">
         <v>Normal</v>
@@ -7562,13 +7550,13 @@
     </row>
     <row r="220">
       <c r="A220">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B220">
-        <v>339042</v>
+        <v>335782</v>
       </c>
       <c r="C220">
-        <v>169.521</v>
+        <v>167.891</v>
       </c>
       <c r="D220" t="str">
         <v>Normal</v>
@@ -7576,13 +7564,13 @@
     </row>
     <row r="221">
       <c r="A221">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B221">
-        <v>340742</v>
+        <v>337382</v>
       </c>
       <c r="C221">
-        <v>170.371</v>
+        <v>168.691</v>
       </c>
       <c r="D221" t="str">
         <v>Normal</v>
@@ -7590,13 +7578,13 @@
     </row>
     <row r="222">
       <c r="A222">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B222">
-        <v>342372</v>
+        <v>339042</v>
       </c>
       <c r="C222">
-        <v>171.186</v>
+        <v>169.521</v>
       </c>
       <c r="D222" t="str">
         <v>Normal</v>
@@ -7604,13 +7592,13 @@
     </row>
     <row r="223">
       <c r="A223">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B223">
-        <v>343950</v>
+        <v>340742</v>
       </c>
       <c r="C223">
-        <v>171.975</v>
+        <v>170.371</v>
       </c>
       <c r="D223" t="str">
         <v>Normal</v>
@@ -7618,13 +7606,13 @@
     </row>
     <row r="224">
       <c r="A224">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B224">
-        <v>345540</v>
+        <v>342372</v>
       </c>
       <c r="C224">
-        <v>172.77</v>
+        <v>171.186</v>
       </c>
       <c r="D224" t="str">
         <v>Normal</v>
@@ -7632,13 +7620,13 @@
     </row>
     <row r="225">
       <c r="A225">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B225">
-        <v>347090</v>
+        <v>343950</v>
       </c>
       <c r="C225">
-        <v>173.545</v>
+        <v>171.975</v>
       </c>
       <c r="D225" t="str">
         <v>Normal</v>
@@ -7646,13 +7634,13 @@
     </row>
     <row r="226">
       <c r="A226">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B226">
-        <v>348600</v>
+        <v>345540</v>
       </c>
       <c r="C226">
-        <v>174.3</v>
+        <v>172.77</v>
       </c>
       <c r="D226" t="str">
         <v>Normal</v>
@@ -7660,13 +7648,13 @@
     </row>
     <row r="227">
       <c r="A227">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B227">
-        <v>350130</v>
+        <v>347090</v>
       </c>
       <c r="C227">
-        <v>175.065</v>
+        <v>173.545</v>
       </c>
       <c r="D227" t="str">
         <v>Normal</v>
@@ -7674,13 +7662,13 @@
     </row>
     <row r="228">
       <c r="A228">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B228">
-        <v>351670</v>
+        <v>348600</v>
       </c>
       <c r="C228">
-        <v>175.835</v>
+        <v>174.3</v>
       </c>
       <c r="D228" t="str">
         <v>Normal</v>
@@ -7688,13 +7676,13 @@
     </row>
     <row r="229">
       <c r="A229">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B229">
-        <v>353240</v>
+        <v>350130</v>
       </c>
       <c r="C229">
-        <v>176.62</v>
+        <v>175.065</v>
       </c>
       <c r="D229" t="str">
         <v>Normal</v>
@@ -7702,13 +7690,13 @@
     </row>
     <row r="230">
       <c r="A230">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B230">
-        <v>354880</v>
+        <v>351670</v>
       </c>
       <c r="C230">
-        <v>177.44</v>
+        <v>175.835</v>
       </c>
       <c r="D230" t="str">
         <v>Normal</v>
@@ -7716,13 +7704,13 @@
     </row>
     <row r="231">
       <c r="A231">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B231">
-        <v>356530</v>
+        <v>353240</v>
       </c>
       <c r="C231">
-        <v>178.265</v>
+        <v>176.62</v>
       </c>
       <c r="D231" t="str">
         <v>Normal</v>
@@ -7730,13 +7718,13 @@
     </row>
     <row r="232">
       <c r="A232">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B232">
-        <v>358170</v>
+        <v>354880</v>
       </c>
       <c r="C232">
-        <v>179.085</v>
+        <v>177.44</v>
       </c>
       <c r="D232" t="str">
         <v>Normal</v>
@@ -7744,13 +7732,13 @@
     </row>
     <row r="233">
       <c r="A233">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B233">
-        <v>359830</v>
+        <v>356530</v>
       </c>
       <c r="C233">
-        <v>179.915</v>
+        <v>178.265</v>
       </c>
       <c r="D233" t="str">
         <v>Normal</v>
@@ -7758,13 +7746,13 @@
     </row>
     <row r="234">
       <c r="A234">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B234">
-        <v>361440</v>
+        <v>358170</v>
       </c>
       <c r="C234">
-        <v>180.72</v>
+        <v>179.085</v>
       </c>
       <c r="D234" t="str">
         <v>Normal</v>
@@ -7772,13 +7760,13 @@
     </row>
     <row r="235">
       <c r="A235">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B235">
-        <v>363010</v>
+        <v>359830</v>
       </c>
       <c r="C235">
-        <v>181.505</v>
+        <v>179.915</v>
       </c>
       <c r="D235" t="str">
         <v>Normal</v>
@@ -7786,13 +7774,13 @@
     </row>
     <row r="236">
       <c r="A236">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B236">
-        <v>364510</v>
+        <v>361440</v>
       </c>
       <c r="C236">
-        <v>182.255</v>
+        <v>180.72</v>
       </c>
       <c r="D236" t="str">
         <v>Normal</v>
@@ -7800,13 +7788,13 @@
     </row>
     <row r="237">
       <c r="A237">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B237">
-        <v>366020</v>
+        <v>363010</v>
       </c>
       <c r="C237">
-        <v>183.01</v>
+        <v>181.505</v>
       </c>
       <c r="D237" t="str">
         <v>Normal</v>
@@ -7814,13 +7802,13 @@
     </row>
     <row r="238">
       <c r="A238">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B238">
-        <v>367540</v>
+        <v>364510</v>
       </c>
       <c r="C238">
-        <v>183.77</v>
+        <v>182.255</v>
       </c>
       <c r="D238" t="str">
         <v>Normal</v>
@@ -7828,13 +7816,13 @@
     </row>
     <row r="239">
       <c r="A239">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B239">
-        <v>369100</v>
+        <v>366020</v>
       </c>
       <c r="C239">
-        <v>184.55</v>
+        <v>183.01</v>
       </c>
       <c r="D239" t="str">
         <v>Normal</v>
@@ -7842,13 +7830,13 @@
     </row>
     <row r="240">
       <c r="A240">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B240">
-        <v>370730</v>
+        <v>367540</v>
       </c>
       <c r="C240">
-        <v>185.365</v>
+        <v>183.77</v>
       </c>
       <c r="D240" t="str">
         <v>Normal</v>
@@ -7856,13 +7844,13 @@
     </row>
     <row r="241">
       <c r="A241">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B241">
-        <v>372380</v>
+        <v>369100</v>
       </c>
       <c r="C241">
-        <v>186.19</v>
+        <v>184.55</v>
       </c>
       <c r="D241" t="str">
         <v>Normal</v>
@@ -7870,13 +7858,13 @@
     </row>
     <row r="242">
       <c r="A242">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B242">
-        <v>374070</v>
+        <v>370730</v>
       </c>
       <c r="C242">
-        <v>187.035</v>
+        <v>185.365</v>
       </c>
       <c r="D242" t="str">
         <v>Normal</v>
@@ -7884,13 +7872,13 @@
     </row>
     <row r="243">
       <c r="A243">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B243">
-        <v>375740</v>
+        <v>372380</v>
       </c>
       <c r="C243">
-        <v>187.87</v>
+        <v>186.19</v>
       </c>
       <c r="D243" t="str">
         <v>Normal</v>
@@ -7898,13 +7886,13 @@
     </row>
     <row r="244">
       <c r="A244">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B244">
-        <v>377420</v>
+        <v>374070</v>
       </c>
       <c r="C244">
-        <v>188.71</v>
+        <v>187.035</v>
       </c>
       <c r="D244" t="str">
         <v>Normal</v>
@@ -7912,13 +7900,13 @@
     </row>
     <row r="245">
       <c r="A245">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B245">
-        <v>378970</v>
+        <v>375740</v>
       </c>
       <c r="C245">
-        <v>189.485</v>
+        <v>187.87</v>
       </c>
       <c r="D245" t="str">
         <v>Normal</v>
@@ -7926,13 +7914,13 @@
     </row>
     <row r="246">
       <c r="A246">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B246">
-        <v>380530</v>
+        <v>377420</v>
       </c>
       <c r="C246">
-        <v>190.265</v>
+        <v>188.71</v>
       </c>
       <c r="D246" t="str">
         <v>Normal</v>
@@ -7940,13 +7928,13 @@
     </row>
     <row r="247">
       <c r="A247">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B247">
-        <v>382050</v>
+        <v>378970</v>
       </c>
       <c r="C247">
-        <v>191.025</v>
+        <v>189.485</v>
       </c>
       <c r="D247" t="str">
         <v>Normal</v>
@@ -7954,13 +7942,13 @@
     </row>
     <row r="248">
       <c r="A248">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B248">
-        <v>383571</v>
+        <v>380530</v>
       </c>
       <c r="C248">
-        <v>191.786</v>
+        <v>190.265</v>
       </c>
       <c r="D248" t="str">
         <v>Normal</v>
@@ -7968,13 +7956,13 @@
     </row>
     <row r="249">
       <c r="A249">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B249">
-        <v>385100</v>
+        <v>382050</v>
       </c>
       <c r="C249">
-        <v>192.55</v>
+        <v>191.025</v>
       </c>
       <c r="D249" t="str">
         <v>Normal</v>
@@ -7982,13 +7970,13 @@
     </row>
     <row r="250">
       <c r="A250">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B250">
-        <v>386700</v>
+        <v>383571</v>
       </c>
       <c r="C250">
-        <v>193.35</v>
+        <v>191.786</v>
       </c>
       <c r="D250" t="str">
         <v>Normal</v>
@@ -7996,13 +7984,13 @@
     </row>
     <row r="251">
       <c r="A251">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B251">
-        <v>388370</v>
+        <v>385100</v>
       </c>
       <c r="C251">
-        <v>194.185</v>
+        <v>192.55</v>
       </c>
       <c r="D251" t="str">
         <v>Normal</v>
@@ -8010,13 +7998,13 @@
     </row>
     <row r="252">
       <c r="A252">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B252">
-        <v>390040</v>
+        <v>386700</v>
       </c>
       <c r="C252">
-        <v>195.02</v>
+        <v>193.35</v>
       </c>
       <c r="D252" t="str">
         <v>Normal</v>
@@ -8024,13 +8012,13 @@
     </row>
     <row r="253">
       <c r="A253">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B253">
-        <v>391720</v>
+        <v>388370</v>
       </c>
       <c r="C253">
-        <v>195.86</v>
+        <v>194.185</v>
       </c>
       <c r="D253" t="str">
         <v>Normal</v>
@@ -8038,13 +8026,13 @@
     </row>
     <row r="254">
       <c r="A254">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B254">
-        <v>393360</v>
+        <v>390040</v>
       </c>
       <c r="C254">
-        <v>196.68</v>
+        <v>195.02</v>
       </c>
       <c r="D254" t="str">
         <v>Normal</v>
@@ -8052,13 +8040,13 @@
     </row>
     <row r="255">
       <c r="A255">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B255">
-        <v>394990</v>
+        <v>391720</v>
       </c>
       <c r="C255">
-        <v>197.495</v>
+        <v>195.86</v>
       </c>
       <c r="D255" t="str">
         <v>Normal</v>
@@ -8066,13 +8054,13 @@
     </row>
     <row r="256">
       <c r="A256">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B256">
-        <v>396550</v>
+        <v>393360</v>
       </c>
       <c r="C256">
-        <v>198.275</v>
+        <v>196.68</v>
       </c>
       <c r="D256" t="str">
         <v>Normal</v>
@@ -8080,13 +8068,13 @@
     </row>
     <row r="257">
       <c r="A257">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B257">
-        <v>398020</v>
+        <v>394990</v>
       </c>
       <c r="C257">
-        <v>199.01</v>
+        <v>197.495</v>
       </c>
       <c r="D257" t="str">
         <v>Normal</v>
@@ -8094,13 +8082,13 @@
     </row>
     <row r="258">
       <c r="A258">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B258">
-        <v>399530</v>
+        <v>396550</v>
       </c>
       <c r="C258">
-        <v>199.765</v>
+        <v>198.275</v>
       </c>
       <c r="D258" t="str">
         <v>Normal</v>
@@ -8108,13 +8096,13 @@
     </row>
     <row r="259">
       <c r="A259">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B259">
-        <v>401020</v>
+        <v>398020</v>
       </c>
       <c r="C259">
-        <v>200.51</v>
+        <v>199.01</v>
       </c>
       <c r="D259" t="str">
         <v>Normal</v>
@@ -8122,13 +8110,13 @@
     </row>
     <row r="260">
       <c r="A260">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B260">
-        <v>402530</v>
+        <v>399530</v>
       </c>
       <c r="C260">
-        <v>201.265</v>
+        <v>199.765</v>
       </c>
       <c r="D260" t="str">
         <v>Normal</v>
@@ -8136,13 +8124,13 @@
     </row>
     <row r="261">
       <c r="A261">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B261">
-        <v>404150</v>
+        <v>401020</v>
       </c>
       <c r="C261">
-        <v>202.075</v>
+        <v>200.51</v>
       </c>
       <c r="D261" t="str">
         <v>Normal</v>
@@ -8150,13 +8138,13 @@
     </row>
     <row r="262">
       <c r="A262">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B262">
-        <v>405850</v>
+        <v>402530</v>
       </c>
       <c r="C262">
-        <v>202.925</v>
+        <v>201.265</v>
       </c>
       <c r="D262" t="str">
         <v>Normal</v>
@@ -8164,13 +8152,13 @@
     </row>
     <row r="263">
       <c r="A263">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B263">
-        <v>407530</v>
+        <v>404150</v>
       </c>
       <c r="C263">
-        <v>203.765</v>
+        <v>202.075</v>
       </c>
       <c r="D263" t="str">
         <v>Normal</v>
@@ -8178,13 +8166,13 @@
     </row>
     <row r="264">
       <c r="A264">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B264">
-        <v>409170</v>
+        <v>405850</v>
       </c>
       <c r="C264">
-        <v>204.585</v>
+        <v>202.925</v>
       </c>
       <c r="D264" t="str">
         <v>Normal</v>
@@ -8192,13 +8180,13 @@
     </row>
     <row r="265">
       <c r="A265">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B265">
-        <v>410770</v>
+        <v>407530</v>
       </c>
       <c r="C265">
-        <v>205.385</v>
+        <v>203.765</v>
       </c>
       <c r="D265" t="str">
         <v>Normal</v>
@@ -8206,13 +8194,13 @@
     </row>
     <row r="266">
       <c r="A266">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B266">
-        <v>412380</v>
+        <v>409170</v>
       </c>
       <c r="C266">
-        <v>206.19</v>
+        <v>204.585</v>
       </c>
       <c r="D266" t="str">
         <v>Normal</v>
@@ -8220,13 +8208,13 @@
     </row>
     <row r="267">
       <c r="A267">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B267">
-        <v>413920</v>
+        <v>410770</v>
       </c>
       <c r="C267">
-        <v>206.96</v>
+        <v>205.385</v>
       </c>
       <c r="D267" t="str">
         <v>Normal</v>
@@ -8234,13 +8222,13 @@
     </row>
     <row r="268">
       <c r="A268">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B268">
-        <v>415440</v>
+        <v>412380</v>
       </c>
       <c r="C268">
-        <v>207.72</v>
+        <v>206.19</v>
       </c>
       <c r="D268" t="str">
         <v>Normal</v>
@@ -8248,13 +8236,13 @@
     </row>
     <row r="269">
       <c r="A269">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B269">
-        <v>416970</v>
+        <v>413920</v>
       </c>
       <c r="C269">
-        <v>208.485</v>
+        <v>206.96</v>
       </c>
       <c r="D269" t="str">
         <v>Normal</v>
@@ -8262,13 +8250,13 @@
     </row>
     <row r="270">
       <c r="A270">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B270">
-        <v>418530</v>
+        <v>415440</v>
       </c>
       <c r="C270">
-        <v>209.265</v>
+        <v>207.72</v>
       </c>
       <c r="D270" t="str">
         <v>Normal</v>
@@ -8276,13 +8264,13 @@
     </row>
     <row r="271">
       <c r="A271">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B271">
-        <v>420160</v>
+        <v>416970</v>
       </c>
       <c r="C271">
-        <v>210.08</v>
+        <v>208.485</v>
       </c>
       <c r="D271" t="str">
         <v>Normal</v>
@@ -8290,13 +8278,13 @@
     </row>
     <row r="272">
       <c r="A272">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B272">
-        <v>421830</v>
+        <v>418530</v>
       </c>
       <c r="C272">
-        <v>210.915</v>
+        <v>209.265</v>
       </c>
       <c r="D272" t="str">
         <v>Normal</v>
@@ -8304,13 +8292,13 @@
     </row>
     <row r="273">
       <c r="A273">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B273">
-        <v>423510</v>
+        <v>420160</v>
       </c>
       <c r="C273">
-        <v>211.755</v>
+        <v>210.08</v>
       </c>
       <c r="D273" t="str">
         <v>Normal</v>
@@ -8318,13 +8306,13 @@
     </row>
     <row r="274">
       <c r="A274">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B274">
-        <v>425160</v>
+        <v>421830</v>
       </c>
       <c r="C274">
-        <v>212.58</v>
+        <v>210.915</v>
       </c>
       <c r="D274" t="str">
         <v>Normal</v>
@@ -8332,13 +8320,13 @@
     </row>
     <row r="275">
       <c r="A275">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B275">
-        <v>426820</v>
+        <v>423510</v>
       </c>
       <c r="C275">
-        <v>213.41</v>
+        <v>211.755</v>
       </c>
       <c r="D275" t="str">
         <v>Normal</v>
@@ -8346,13 +8334,13 @@
     </row>
     <row r="276">
       <c r="A276">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B276">
-        <v>428410</v>
+        <v>425160</v>
       </c>
       <c r="C276">
-        <v>214.205</v>
+        <v>212.58</v>
       </c>
       <c r="D276" t="str">
         <v>Normal</v>
@@ -8360,13 +8348,13 @@
     </row>
     <row r="277">
       <c r="A277">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B277">
-        <v>429982</v>
+        <v>426820</v>
       </c>
       <c r="C277">
-        <v>214.991</v>
+        <v>213.41</v>
       </c>
       <c r="D277" t="str">
         <v>Normal</v>
@@ -8374,13 +8362,13 @@
     </row>
     <row r="278">
       <c r="A278">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B278">
-        <v>431473</v>
+        <v>428410</v>
       </c>
       <c r="C278">
-        <v>215.737</v>
+        <v>214.205</v>
       </c>
       <c r="D278" t="str">
         <v>Normal</v>
@@ -8388,13 +8376,13 @@
     </row>
     <row r="279">
       <c r="A279">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B279">
-        <v>432992</v>
+        <v>429982</v>
       </c>
       <c r="C279">
-        <v>216.496</v>
+        <v>214.991</v>
       </c>
       <c r="D279" t="str">
         <v>Normal</v>
@@ -8402,13 +8390,13 @@
     </row>
     <row r="280">
       <c r="A280">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B280">
-        <v>434542</v>
+        <v>431473</v>
       </c>
       <c r="C280">
-        <v>217.271</v>
+        <v>215.737</v>
       </c>
       <c r="D280" t="str">
         <v>Normal</v>
@@ -8416,13 +8404,13 @@
     </row>
     <row r="281">
       <c r="A281">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B281">
-        <v>436092</v>
+        <v>432992</v>
       </c>
       <c r="C281">
-        <v>218.046</v>
+        <v>216.496</v>
       </c>
       <c r="D281" t="str">
         <v>Normal</v>
@@ -8430,13 +8418,13 @@
     </row>
     <row r="282">
       <c r="A282">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B282">
-        <v>437772</v>
+        <v>434542</v>
       </c>
       <c r="C282">
-        <v>218.886</v>
+        <v>217.271</v>
       </c>
       <c r="D282" t="str">
         <v>Normal</v>
@@ -8444,13 +8432,13 @@
     </row>
     <row r="283">
       <c r="A283">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B283">
-        <v>439472</v>
+        <v>436092</v>
       </c>
       <c r="C283">
-        <v>219.736</v>
+        <v>218.046</v>
       </c>
       <c r="D283" t="str">
         <v>Normal</v>
@@ -8458,13 +8446,13 @@
     </row>
     <row r="284">
       <c r="A284">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B284">
-        <v>441142</v>
+        <v>437772</v>
       </c>
       <c r="C284">
-        <v>220.571</v>
+        <v>218.886</v>
       </c>
       <c r="D284" t="str">
         <v>Normal</v>
@@ -8472,13 +8460,13 @@
     </row>
     <row r="285">
       <c r="A285">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B285">
-        <v>442822</v>
+        <v>439472</v>
       </c>
       <c r="C285">
-        <v>221.411</v>
+        <v>219.736</v>
       </c>
       <c r="D285" t="str">
         <v>Normal</v>
@@ -8486,13 +8474,13 @@
     </row>
     <row r="286">
       <c r="A286">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B286">
-        <v>444453</v>
+        <v>441142</v>
       </c>
       <c r="C286">
-        <v>222.227</v>
+        <v>220.571</v>
       </c>
       <c r="D286" t="str">
         <v>Normal</v>
@@ -8500,13 +8488,13 @@
     </row>
     <row r="287">
       <c r="A287">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B287">
-        <v>445972</v>
+        <v>442822</v>
       </c>
       <c r="C287">
-        <v>222.986</v>
+        <v>221.411</v>
       </c>
       <c r="D287" t="str">
         <v>Normal</v>
@@ -8514,13 +8502,13 @@
     </row>
     <row r="288">
       <c r="A288">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B288">
-        <v>447512</v>
+        <v>444453</v>
       </c>
       <c r="C288">
-        <v>223.756</v>
+        <v>222.227</v>
       </c>
       <c r="D288" t="str">
         <v>Normal</v>
@@ -8528,13 +8516,13 @@
     </row>
     <row r="289">
       <c r="A289">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B289">
-        <v>449032</v>
+        <v>445972</v>
       </c>
       <c r="C289">
-        <v>224.516</v>
+        <v>222.986</v>
       </c>
       <c r="D289" t="str">
         <v>Normal</v>
@@ -8542,13 +8530,13 @@
     </row>
     <row r="290">
       <c r="A290">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B290">
-        <v>450563</v>
+        <v>447512</v>
       </c>
       <c r="C290">
-        <v>225.282</v>
+        <v>223.756</v>
       </c>
       <c r="D290" t="str">
         <v>Normal</v>
@@ -8556,13 +8544,13 @@
     </row>
     <row r="291">
       <c r="A291">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B291">
-        <v>452103</v>
+        <v>449032</v>
       </c>
       <c r="C291">
-        <v>226.052</v>
+        <v>224.516</v>
       </c>
       <c r="D291" t="str">
         <v>Normal</v>
@@ -8570,13 +8558,13 @@
     </row>
     <row r="292">
       <c r="A292">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B292">
-        <v>453712</v>
+        <v>450563</v>
       </c>
       <c r="C292">
-        <v>226.856</v>
+        <v>225.282</v>
       </c>
       <c r="D292" t="str">
         <v>Normal</v>
@@ -8584,13 +8572,13 @@
     </row>
     <row r="293">
       <c r="A293">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B293">
-        <v>455362</v>
+        <v>452103</v>
       </c>
       <c r="C293">
-        <v>227.681</v>
+        <v>226.052</v>
       </c>
       <c r="D293" t="str">
         <v>Normal</v>
@@ -8598,13 +8586,13 @@
     </row>
     <row r="294">
       <c r="A294">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B294">
-        <v>457072</v>
+        <v>453712</v>
       </c>
       <c r="C294">
-        <v>228.536</v>
+        <v>226.856</v>
       </c>
       <c r="D294" t="str">
         <v>Normal</v>
@@ -8612,13 +8600,13 @@
     </row>
     <row r="295">
       <c r="A295">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B295">
-        <v>458752</v>
+        <v>455362</v>
       </c>
       <c r="C295">
-        <v>229.376</v>
+        <v>227.681</v>
       </c>
       <c r="D295" t="str">
         <v>Normal</v>
@@ -8626,13 +8614,13 @@
     </row>
     <row r="296">
       <c r="A296">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B296">
-        <v>460392</v>
+        <v>457072</v>
       </c>
       <c r="C296">
-        <v>230.196</v>
+        <v>228.536</v>
       </c>
       <c r="D296" t="str">
         <v>Normal</v>
@@ -8640,13 +8628,13 @@
     </row>
     <row r="297">
       <c r="A297">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B297">
-        <v>462032</v>
+        <v>458752</v>
       </c>
       <c r="C297">
-        <v>231.016</v>
+        <v>229.376</v>
       </c>
       <c r="D297" t="str">
         <v>Normal</v>
@@ -8654,13 +8642,13 @@
     </row>
     <row r="298">
       <c r="A298">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B298">
-        <v>463572</v>
+        <v>460392</v>
       </c>
       <c r="C298">
-        <v>231.786</v>
+        <v>230.196</v>
       </c>
       <c r="D298" t="str">
         <v>Normal</v>
@@ -8668,13 +8656,13 @@
     </row>
     <row r="299">
       <c r="A299">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B299">
-        <v>465083</v>
+        <v>462032</v>
       </c>
       <c r="C299">
-        <v>232.542</v>
+        <v>231.016</v>
       </c>
       <c r="D299" t="str">
         <v>Normal</v>
@@ -8682,13 +8670,13 @@
     </row>
     <row r="300">
       <c r="A300">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B300">
-        <v>466563</v>
+        <v>463572</v>
       </c>
       <c r="C300">
-        <v>233.282</v>
+        <v>231.786</v>
       </c>
       <c r="D300" t="str">
         <v>Normal</v>
@@ -8696,13 +8684,13 @@
     </row>
     <row r="301">
       <c r="A301">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B301">
-        <v>468152</v>
+        <v>465083</v>
       </c>
       <c r="C301">
-        <v>234.076</v>
+        <v>232.542</v>
       </c>
       <c r="D301" t="str">
         <v>Normal</v>
@@ -8710,13 +8698,13 @@
     </row>
     <row r="302">
       <c r="A302">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B302">
-        <v>469762</v>
+        <v>466563</v>
       </c>
       <c r="C302">
-        <v>234.881</v>
+        <v>233.282</v>
       </c>
       <c r="D302" t="str">
         <v>Normal</v>
@@ -8724,13 +8712,13 @@
     </row>
     <row r="303">
       <c r="A303">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B303">
-        <v>471422</v>
+        <v>468152</v>
       </c>
       <c r="C303">
-        <v>235.711</v>
+        <v>234.076</v>
       </c>
       <c r="D303" t="str">
         <v>Normal</v>
@@ -8738,13 +8726,13 @@
     </row>
     <row r="304">
       <c r="A304">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B304">
-        <v>473106</v>
+        <v>469762</v>
       </c>
       <c r="C304">
-        <v>236.553</v>
+        <v>234.881</v>
       </c>
       <c r="D304" t="str">
         <v>Normal</v>
@@ -8752,13 +8740,13 @@
     </row>
     <row r="305">
       <c r="A305">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B305">
-        <v>474786</v>
+        <v>471422</v>
       </c>
       <c r="C305">
-        <v>237.393</v>
+        <v>235.711</v>
       </c>
       <c r="D305" t="str">
         <v>Normal</v>
@@ -8766,13 +8754,13 @@
     </row>
     <row r="306">
       <c r="A306">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B306">
-        <v>476447</v>
+        <v>473106</v>
       </c>
       <c r="C306">
-        <v>238.224</v>
+        <v>236.553</v>
       </c>
       <c r="D306" t="str">
         <v>Normal</v>
@@ -8780,13 +8768,13 @@
     </row>
     <row r="307">
       <c r="A307">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B307">
-        <v>478067</v>
+        <v>474786</v>
       </c>
       <c r="C307">
-        <v>239.034</v>
+        <v>237.393</v>
       </c>
       <c r="D307" t="str">
         <v>Normal</v>
@@ -8794,13 +8782,13 @@
     </row>
     <row r="308">
       <c r="A308">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B308">
-        <v>479636</v>
+        <v>476447</v>
       </c>
       <c r="C308">
-        <v>239.818</v>
+        <v>238.224</v>
       </c>
       <c r="D308" t="str">
         <v>Normal</v>
@@ -8808,13 +8796,13 @@
     </row>
     <row r="309">
       <c r="A309">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B309">
-        <v>481176</v>
+        <v>478067</v>
       </c>
       <c r="C309">
-        <v>240.588</v>
+        <v>239.034</v>
       </c>
       <c r="D309" t="str">
         <v>Normal</v>
@@ -8822,13 +8810,13 @@
     </row>
     <row r="310">
       <c r="A310">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B310">
-        <v>482727</v>
+        <v>479636</v>
       </c>
       <c r="C310">
-        <v>241.364</v>
+        <v>239.818</v>
       </c>
       <c r="D310" t="str">
         <v>Normal</v>
@@ -8836,13 +8824,13 @@
     </row>
     <row r="311">
       <c r="A311">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B311">
-        <v>484276</v>
+        <v>481176</v>
       </c>
       <c r="C311">
-        <v>242.138</v>
+        <v>240.588</v>
       </c>
       <c r="D311" t="str">
         <v>Normal</v>
@@ -8850,13 +8838,13 @@
     </row>
     <row r="312">
       <c r="A312">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B312">
-        <v>485837</v>
+        <v>482727</v>
       </c>
       <c r="C312">
-        <v>242.919</v>
+        <v>241.364</v>
       </c>
       <c r="D312" t="str">
         <v>Normal</v>
@@ -8864,13 +8852,13 @@
     </row>
     <row r="313">
       <c r="A313">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B313">
-        <v>487437</v>
+        <v>484276</v>
       </c>
       <c r="C313">
-        <v>243.719</v>
+        <v>242.138</v>
       </c>
       <c r="D313" t="str">
         <v>Normal</v>
@@ -8878,13 +8866,13 @@
     </row>
     <row r="314">
       <c r="A314">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B314">
-        <v>489086</v>
+        <v>485837</v>
       </c>
       <c r="C314">
-        <v>244.543</v>
+        <v>242.919</v>
       </c>
       <c r="D314" t="str">
         <v>Normal</v>
@@ -8892,13 +8880,13 @@
     </row>
     <row r="315">
       <c r="A315">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B315">
-        <v>490797</v>
+        <v>487437</v>
       </c>
       <c r="C315">
-        <v>245.399</v>
+        <v>243.719</v>
       </c>
       <c r="D315" t="str">
         <v>Normal</v>
@@ -8906,13 +8894,13 @@
     </row>
     <row r="316">
       <c r="A316">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B316">
-        <v>492487</v>
+        <v>489086</v>
       </c>
       <c r="C316">
-        <v>246.244</v>
+        <v>244.543</v>
       </c>
       <c r="D316" t="str">
         <v>Normal</v>
@@ -8920,13 +8908,13 @@
     </row>
     <row r="317">
       <c r="A317">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B317">
-        <v>494127</v>
+        <v>490797</v>
       </c>
       <c r="C317">
-        <v>247.064</v>
+        <v>245.399</v>
       </c>
       <c r="D317" t="str">
         <v>Normal</v>
@@ -8934,13 +8922,13 @@
     </row>
     <row r="318">
       <c r="A318">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B318">
-        <v>495717</v>
+        <v>492487</v>
       </c>
       <c r="C318">
-        <v>247.859</v>
+        <v>246.244</v>
       </c>
       <c r="D318" t="str">
         <v>Normal</v>
@@ -8948,13 +8936,13 @@
     </row>
     <row r="319">
       <c r="A319">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B319">
-        <v>497246</v>
+        <v>494127</v>
       </c>
       <c r="C319">
-        <v>248.623</v>
+        <v>247.064</v>
       </c>
       <c r="D319" t="str">
         <v>Normal</v>
@@ -8962,13 +8950,13 @@
     </row>
     <row r="320">
       <c r="A320">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B320">
-        <v>498766</v>
+        <v>495717</v>
       </c>
       <c r="C320">
-        <v>249.383</v>
+        <v>247.859</v>
       </c>
       <c r="D320" t="str">
         <v>Normal</v>
@@ -8976,13 +8964,13 @@
     </row>
     <row r="321">
       <c r="A321">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B321">
-        <v>500307</v>
+        <v>497246</v>
       </c>
       <c r="C321">
-        <v>250.154</v>
+        <v>248.623</v>
       </c>
       <c r="D321" t="str">
         <v>Normal</v>
@@ -8990,13 +8978,13 @@
     </row>
     <row r="322">
       <c r="A322">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B322">
-        <v>501847</v>
+        <v>498766</v>
       </c>
       <c r="C322">
-        <v>250.924</v>
+        <v>249.383</v>
       </c>
       <c r="D322" t="str">
         <v>Normal</v>
@@ -9004,13 +8992,13 @@
     </row>
     <row r="323">
       <c r="A323">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B323">
-        <v>503436</v>
+        <v>500307</v>
       </c>
       <c r="C323">
-        <v>251.718</v>
+        <v>250.154</v>
       </c>
       <c r="D323" t="str">
         <v>Normal</v>
@@ -9018,13 +9006,13 @@
     </row>
     <row r="324">
       <c r="A324">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B324">
-        <v>505067</v>
+        <v>501847</v>
       </c>
       <c r="C324">
-        <v>252.534</v>
+        <v>250.924</v>
       </c>
       <c r="D324" t="str">
         <v>Normal</v>
@@ -9032,13 +9020,13 @@
     </row>
     <row r="325">
       <c r="A325">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B325">
-        <v>506746</v>
+        <v>503436</v>
       </c>
       <c r="C325">
-        <v>253.373</v>
+        <v>251.718</v>
       </c>
       <c r="D325" t="str">
         <v>Normal</v>
@@ -9046,13 +9034,13 @@
     </row>
     <row r="326">
       <c r="A326">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B326">
-        <v>508386</v>
+        <v>505067</v>
       </c>
       <c r="C326">
-        <v>254.193</v>
+        <v>252.534</v>
       </c>
       <c r="D326" t="str">
         <v>Normal</v>
@@ -9060,13 +9048,13 @@
     </row>
     <row r="327">
       <c r="A327">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B327">
-        <v>510037</v>
+        <v>506746</v>
       </c>
       <c r="C327">
-        <v>255.019</v>
+        <v>253.373</v>
       </c>
       <c r="D327" t="str">
         <v>Normal</v>
@@ -9074,13 +9062,13 @@
     </row>
     <row r="328">
       <c r="A328">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B328">
-        <v>511637</v>
+        <v>508386</v>
       </c>
       <c r="C328">
-        <v>255.819</v>
+        <v>254.193</v>
       </c>
       <c r="D328" t="str">
         <v>Normal</v>
@@ -9088,13 +9076,13 @@
     </row>
     <row r="329">
       <c r="A329">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B329">
-        <v>513227</v>
+        <v>510037</v>
       </c>
       <c r="C329">
-        <v>256.614</v>
+        <v>255.019</v>
       </c>
       <c r="D329" t="str">
         <v>Normal</v>
@@ -9102,13 +9090,13 @@
     </row>
     <row r="330">
       <c r="A330">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B330">
-        <v>514743</v>
+        <v>511637</v>
       </c>
       <c r="C330">
-        <v>257.372</v>
+        <v>255.819</v>
       </c>
       <c r="D330" t="str">
         <v>Normal</v>
@@ -9116,13 +9104,13 @@
     </row>
     <row r="331">
       <c r="A331">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B331">
-        <v>516273</v>
+        <v>513227</v>
       </c>
       <c r="C331">
-        <v>258.137</v>
+        <v>256.614</v>
       </c>
       <c r="D331" t="str">
         <v>Normal</v>
@@ -9130,13 +9118,13 @@
     </row>
     <row r="332">
       <c r="A332">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B332">
-        <v>517843</v>
+        <v>514743</v>
       </c>
       <c r="C332">
-        <v>258.921</v>
+        <v>257.372</v>
       </c>
       <c r="D332" t="str">
         <v>Normal</v>
@@ -9144,13 +9132,13 @@
     </row>
     <row r="333">
       <c r="A333">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B333">
-        <v>519404</v>
+        <v>516273</v>
       </c>
       <c r="C333">
-        <v>259.702</v>
+        <v>258.137</v>
       </c>
       <c r="D333" t="str">
         <v>Normal</v>
@@ -9158,13 +9146,13 @@
     </row>
     <row r="334">
       <c r="A334">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B334">
-        <v>521013</v>
+        <v>517843</v>
       </c>
       <c r="C334">
-        <v>260.507</v>
+        <v>258.921</v>
       </c>
       <c r="D334" t="str">
         <v>Normal</v>
@@ -9172,13 +9160,13 @@
     </row>
     <row r="335">
       <c r="A335">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B335">
-        <v>522673</v>
+        <v>519404</v>
       </c>
       <c r="C335">
-        <v>261.337</v>
+        <v>259.702</v>
       </c>
       <c r="D335" t="str">
         <v>Normal</v>
@@ -9186,13 +9174,13 @@
     </row>
     <row r="336">
       <c r="A336">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B336">
-        <v>524353</v>
+        <v>521013</v>
       </c>
       <c r="C336">
-        <v>262.177</v>
+        <v>260.507</v>
       </c>
       <c r="D336" t="str">
         <v>Normal</v>
@@ -9200,13 +9188,13 @@
     </row>
     <row r="337">
       <c r="A337">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B337">
-        <v>526003</v>
+        <v>522673</v>
       </c>
       <c r="C337">
-        <v>263.002</v>
+        <v>261.337</v>
       </c>
       <c r="D337" t="str">
         <v>Normal</v>
@@ -9214,13 +9202,13 @@
     </row>
     <row r="338">
       <c r="A338">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B338">
-        <v>527653</v>
+        <v>524353</v>
       </c>
       <c r="C338">
-        <v>263.827</v>
+        <v>262.177</v>
       </c>
       <c r="D338" t="str">
         <v>Normal</v>
@@ -9228,13 +9216,13 @@
     </row>
     <row r="339">
       <c r="A339">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B339">
-        <v>529293</v>
+        <v>526003</v>
       </c>
       <c r="C339">
-        <v>264.647</v>
+        <v>263.002</v>
       </c>
       <c r="D339" t="str">
         <v>Normal</v>
@@ -9242,13 +9230,13 @@
     </row>
     <row r="340">
       <c r="A340">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B340">
-        <v>530834</v>
+        <v>527653</v>
       </c>
       <c r="C340">
-        <v>265.417</v>
+        <v>263.827</v>
       </c>
       <c r="D340" t="str">
         <v>Normal</v>
@@ -9256,13 +9244,13 @@
     </row>
     <row r="341">
       <c r="A341">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B341">
-        <v>532354</v>
+        <v>529293</v>
       </c>
       <c r="C341">
-        <v>266.177</v>
+        <v>264.647</v>
       </c>
       <c r="D341" t="str">
         <v>Normal</v>
@@ -9270,13 +9258,13 @@
     </row>
     <row r="342">
       <c r="A342">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B342">
-        <v>533853</v>
+        <v>530834</v>
       </c>
       <c r="C342">
-        <v>266.927</v>
+        <v>265.417</v>
       </c>
       <c r="D342" t="str">
         <v>Normal</v>
@@ -9284,13 +9272,13 @@
     </row>
     <row r="343">
       <c r="A343">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B343">
-        <v>535413</v>
+        <v>532354</v>
       </c>
       <c r="C343">
-        <v>267.707</v>
+        <v>266.177</v>
       </c>
       <c r="D343" t="str">
         <v>Normal</v>
@@ -9298,13 +9286,13 @@
     </row>
     <row r="344">
       <c r="A344">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B344">
-        <v>536974</v>
+        <v>533853</v>
       </c>
       <c r="C344">
-        <v>268.487</v>
+        <v>266.927</v>
       </c>
       <c r="D344" t="str">
         <v>Normal</v>
@@ -9312,13 +9300,13 @@
     </row>
     <row r="345">
       <c r="A345">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B345">
-        <v>538593</v>
+        <v>535413</v>
       </c>
       <c r="C345">
-        <v>269.297</v>
+        <v>267.707</v>
       </c>
       <c r="D345" t="str">
         <v>Normal</v>
@@ -9326,13 +9314,13 @@
     </row>
     <row r="346">
       <c r="A346">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B346">
-        <v>540294</v>
+        <v>536974</v>
       </c>
       <c r="C346">
-        <v>270.147</v>
+        <v>268.487</v>
       </c>
       <c r="D346" t="str">
         <v>Normal</v>
@@ -9340,13 +9328,13 @@
     </row>
     <row r="347">
       <c r="A347">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B347">
-        <v>541953</v>
+        <v>538593</v>
       </c>
       <c r="C347">
-        <v>270.977</v>
+        <v>269.297</v>
       </c>
       <c r="D347" t="str">
         <v>Normal</v>
@@ -9354,13 +9342,13 @@
     </row>
     <row r="348">
       <c r="A348">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B348">
-        <v>543634</v>
+        <v>540294</v>
       </c>
       <c r="C348">
-        <v>271.817</v>
+        <v>270.147</v>
       </c>
       <c r="D348" t="str">
         <v>Normal</v>
@@ -9368,13 +9356,13 @@
     </row>
     <row r="349">
       <c r="A349">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B349">
-        <v>545293</v>
+        <v>541953</v>
       </c>
       <c r="C349">
-        <v>272.647</v>
+        <v>270.977</v>
       </c>
       <c r="D349" t="str">
         <v>Normal</v>
@@ -9382,13 +9370,13 @@
     </row>
     <row r="350">
       <c r="A350">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B350">
-        <v>546863</v>
+        <v>543634</v>
       </c>
       <c r="C350">
-        <v>273.432</v>
+        <v>271.817</v>
       </c>
       <c r="D350" t="str">
         <v>Normal</v>
@@ -9396,13 +9384,13 @@
     </row>
     <row r="351">
       <c r="A351">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B351">
-        <v>548413</v>
+        <v>545293</v>
       </c>
       <c r="C351">
-        <v>274.207</v>
+        <v>272.647</v>
       </c>
       <c r="D351" t="str">
         <v>Normal</v>
@@ -9410,13 +9398,13 @@
     </row>
     <row r="352">
       <c r="A352">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B352">
-        <v>549974</v>
+        <v>546863</v>
       </c>
       <c r="C352">
-        <v>274.987</v>
+        <v>273.432</v>
       </c>
       <c r="D352" t="str">
         <v>Normal</v>
@@ -9424,13 +9412,13 @@
     </row>
     <row r="353">
       <c r="A353">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B353">
-        <v>551513</v>
+        <v>548413</v>
       </c>
       <c r="C353">
-        <v>275.757</v>
+        <v>274.207</v>
       </c>
       <c r="D353" t="str">
         <v>Normal</v>
@@ -9438,13 +9426,13 @@
     </row>
     <row r="354">
       <c r="A354">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B354">
-        <v>553064</v>
+        <v>549974</v>
       </c>
       <c r="C354">
-        <v>276.532</v>
+        <v>274.987</v>
       </c>
       <c r="D354" t="str">
         <v>Normal</v>
@@ -9452,13 +9440,13 @@
     </row>
     <row r="355">
       <c r="A355">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B355">
-        <v>554653</v>
+        <v>551513</v>
       </c>
       <c r="C355">
-        <v>277.327</v>
+        <v>275.757</v>
       </c>
       <c r="D355" t="str">
         <v>Normal</v>
@@ -9466,13 +9454,13 @@
     </row>
     <row r="356">
       <c r="A356">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B356">
-        <v>556314</v>
+        <v>553064</v>
       </c>
       <c r="C356">
-        <v>278.157</v>
+        <v>276.532</v>
       </c>
       <c r="D356" t="str">
         <v>Normal</v>
@@ -9480,13 +9468,13 @@
     </row>
     <row r="357">
       <c r="A357">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B357">
-        <v>558032</v>
+        <v>554653</v>
       </c>
       <c r="C357">
-        <v>279.016</v>
+        <v>277.327</v>
       </c>
       <c r="D357" t="str">
         <v>Normal</v>
@@ -9494,13 +9482,13 @@
     </row>
     <row r="358">
       <c r="A358">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B358">
-        <v>559722</v>
+        <v>556314</v>
       </c>
       <c r="C358">
-        <v>279.861</v>
+        <v>278.157</v>
       </c>
       <c r="D358" t="str">
         <v>Normal</v>
@@ -9508,13 +9496,13 @@
     </row>
     <row r="359">
       <c r="A359">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B359">
-        <v>561342</v>
+        <v>558032</v>
       </c>
       <c r="C359">
-        <v>280.671</v>
+        <v>279.016</v>
       </c>
       <c r="D359" t="str">
         <v>Normal</v>
@@ -9522,13 +9510,13 @@
     </row>
     <row r="360">
       <c r="A360">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B360">
-        <v>562912</v>
+        <v>559722</v>
       </c>
       <c r="C360">
-        <v>281.456</v>
+        <v>279.861</v>
       </c>
       <c r="D360" t="str">
         <v>Normal</v>
@@ -9536,13 +9524,13 @@
     </row>
     <row r="361">
       <c r="A361">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B361">
-        <v>564442</v>
+        <v>561342</v>
       </c>
       <c r="C361">
-        <v>282.221</v>
+        <v>280.671</v>
       </c>
       <c r="D361" t="str">
         <v>Normal</v>
@@ -9550,13 +9538,13 @@
     </row>
     <row r="362">
       <c r="A362">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B362">
-        <v>565972</v>
+        <v>562912</v>
       </c>
       <c r="C362">
-        <v>282.986</v>
+        <v>281.456</v>
       </c>
       <c r="D362" t="str">
         <v>Normal</v>
@@ -9564,13 +9552,13 @@
     </row>
     <row r="363">
       <c r="A363">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B363">
-        <v>567492</v>
+        <v>564442</v>
       </c>
       <c r="C363">
-        <v>283.746</v>
+        <v>282.221</v>
       </c>
       <c r="D363" t="str">
         <v>Normal</v>
@@ -9578,13 +9566,13 @@
     </row>
     <row r="364">
       <c r="A364">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B364">
-        <v>569052</v>
+        <v>565972</v>
       </c>
       <c r="C364">
-        <v>284.526</v>
+        <v>282.986</v>
       </c>
       <c r="D364" t="str">
         <v>Normal</v>
@@ -9592,13 +9580,13 @@
     </row>
     <row r="365">
       <c r="A365">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B365">
-        <v>570653</v>
+        <v>567492</v>
       </c>
       <c r="C365">
-        <v>285.327</v>
+        <v>283.746</v>
       </c>
       <c r="D365" t="str">
         <v>Normal</v>
@@ -9606,13 +9594,13 @@
     </row>
     <row r="366">
       <c r="A366">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B366">
-        <v>572292</v>
+        <v>569052</v>
       </c>
       <c r="C366">
-        <v>286.146</v>
+        <v>284.526</v>
       </c>
       <c r="D366" t="str">
         <v>Normal</v>
@@ -9620,13 +9608,13 @@
     </row>
     <row r="367">
       <c r="A367">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B367">
-        <v>573963</v>
+        <v>570653</v>
       </c>
       <c r="C367">
-        <v>286.982</v>
+        <v>285.327</v>
       </c>
       <c r="D367" t="str">
         <v>Normal</v>
@@ -9634,13 +9622,13 @@
     </row>
     <row r="368">
       <c r="A368">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B368">
-        <v>575652</v>
+        <v>572292</v>
       </c>
       <c r="C368">
-        <v>287.826</v>
+        <v>286.146</v>
       </c>
       <c r="D368" t="str">
         <v>Normal</v>
@@ -9648,13 +9636,13 @@
     </row>
     <row r="369">
       <c r="A369">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B369">
-        <v>577302</v>
+        <v>573963</v>
       </c>
       <c r="C369">
-        <v>288.651</v>
+        <v>286.982</v>
       </c>
       <c r="D369" t="str">
         <v>Normal</v>
@@ -9662,13 +9650,13 @@
     </row>
     <row r="370">
       <c r="A370">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B370">
-        <v>578932</v>
+        <v>575652</v>
       </c>
       <c r="C370">
-        <v>289.466</v>
+        <v>287.826</v>
       </c>
       <c r="D370" t="str">
         <v>Normal</v>
@@ -9676,13 +9664,13 @@
     </row>
     <row r="371">
       <c r="A371">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B371">
-        <v>580542</v>
+        <v>577302</v>
       </c>
       <c r="C371">
-        <v>290.271</v>
+        <v>288.651</v>
       </c>
       <c r="D371" t="str">
         <v>Normal</v>
@@ -9690,13 +9678,13 @@
     </row>
     <row r="372">
       <c r="A372">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B372">
-        <v>582083</v>
+        <v>578932</v>
       </c>
       <c r="C372">
-        <v>291.042</v>
+        <v>289.466</v>
       </c>
       <c r="D372" t="str">
         <v>Normal</v>
@@ -9704,13 +9692,13 @@
     </row>
     <row r="373">
       <c r="A373">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B373">
-        <v>583603</v>
+        <v>580542</v>
       </c>
       <c r="C373">
-        <v>291.802</v>
+        <v>290.271</v>
       </c>
       <c r="D373" t="str">
         <v>Normal</v>
@@ -9718,13 +9706,13 @@
     </row>
     <row r="374">
       <c r="A374">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B374">
-        <v>585102</v>
+        <v>582083</v>
       </c>
       <c r="C374">
-        <v>292.551</v>
+        <v>291.042</v>
       </c>
       <c r="D374" t="str">
         <v>Normal</v>
@@ -9732,13 +9720,13 @@
     </row>
     <row r="375">
       <c r="A375">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B375">
-        <v>586692</v>
+        <v>583603</v>
       </c>
       <c r="C375">
-        <v>293.346</v>
+        <v>291.802</v>
       </c>
       <c r="D375" t="str">
         <v>Normal</v>
@@ -9746,13 +9734,13 @@
     </row>
     <row r="376">
       <c r="A376">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B376">
-        <v>588262</v>
+        <v>585102</v>
       </c>
       <c r="C376">
-        <v>294.131</v>
+        <v>292.551</v>
       </c>
       <c r="D376" t="str">
         <v>Normal</v>
@@ -9760,13 +9748,13 @@
     </row>
     <row r="377">
       <c r="A377">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B377">
-        <v>589892</v>
+        <v>586692</v>
       </c>
       <c r="C377">
-        <v>294.946</v>
+        <v>293.346</v>
       </c>
       <c r="D377" t="str">
         <v>Normal</v>
@@ -9774,13 +9762,13 @@
     </row>
     <row r="378">
       <c r="A378">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B378">
-        <v>591592</v>
+        <v>588262</v>
       </c>
       <c r="C378">
-        <v>295.796</v>
+        <v>294.131</v>
       </c>
       <c r="D378" t="str">
         <v>Normal</v>
@@ -9788,13 +9776,13 @@
     </row>
     <row r="379">
       <c r="A379">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B379">
-        <v>593282</v>
+        <v>589892</v>
       </c>
       <c r="C379">
-        <v>296.641</v>
+        <v>294.946</v>
       </c>
       <c r="D379" t="str">
         <v>Normal</v>
@@ -9802,13 +9790,13 @@
     </row>
     <row r="380">
       <c r="A380">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B380">
-        <v>594912</v>
+        <v>591592</v>
       </c>
       <c r="C380">
-        <v>297.456</v>
+        <v>295.796</v>
       </c>
       <c r="D380" t="str">
         <v>Normal</v>
@@ -9816,13 +9804,13 @@
     </row>
     <row r="381">
       <c r="A381">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B381">
-        <v>596462</v>
+        <v>593282</v>
       </c>
       <c r="C381">
-        <v>298.231</v>
+        <v>296.641</v>
       </c>
       <c r="D381" t="str">
         <v>Normal</v>
@@ -9830,13 +9818,13 @@
     </row>
     <row r="382">
       <c r="A382">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B382">
-        <v>597992</v>
+        <v>594912</v>
       </c>
       <c r="C382">
-        <v>298.996</v>
+        <v>297.456</v>
       </c>
       <c r="D382" t="str">
         <v>Normal</v>
@@ -9844,21 +9832,49 @@
     </row>
     <row r="383">
       <c r="A383">
+        <v>373</v>
+      </c>
+      <c r="B383">
+        <v>596462</v>
+      </c>
+      <c r="C383">
+        <v>298.231</v>
+      </c>
+      <c r="D383" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384">
+        <v>374</v>
+      </c>
+      <c r="B384">
+        <v>597992</v>
+      </c>
+      <c r="C384">
+        <v>298.996</v>
+      </c>
+      <c r="D384" t="str">
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385">
         <v>375</v>
       </c>
-      <c r="B383">
+      <c r="B385">
         <v>599502</v>
       </c>
-      <c r="C383">
+      <c r="C385">
         <v>299.751</v>
       </c>
-      <c r="D383" t="str">
+      <c r="D385" t="str">
         <v>Normal</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D383"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D385"/>
   </ignoredErrors>
 </worksheet>
 </file>